--- a/amir_adv/adv_templates/example.xlsx
+++ b/amir_adv/adv_templates/example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\amir_adv\adv_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAF0170-C731-4805-B37E-F88095F58E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754A1A57-2CD7-4987-AB58-0A44A6A87E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +153,11 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -284,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -338,6 +343,20 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,7 +579,7 @@
     <col min="1" max="1" width="5.8984375" style="26" customWidth="1"/>
     <col min="2" max="2" width="5.19921875" style="26" customWidth="1"/>
     <col min="3" max="3" width="10.19921875" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.3984375" customWidth="1"/>
+    <col min="4" max="4" width="18.8984375" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
     <col min="7" max="7" width="7.8984375" customWidth="1"/>
@@ -662,10 +681,10 @@
       <c r="G2" s="21"/>
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="22">
+      <c r="K2" s="28">
         <v>28118024</v>
       </c>
       <c r="L2" s="21" t="s">
@@ -698,8 +717,8 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="16"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="34"/>
       <c r="L3" s="13"/>
       <c r="M3" s="14"/>
       <c r="N3" s="15"/>
@@ -726,8 +745,8 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="16"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="34"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="16"/>
@@ -754,8 +773,8 @@
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="18"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="34"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="18"/>
@@ -782,8 +801,8 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="16"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="34"/>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
       <c r="N6" s="16"/>
@@ -810,8 +829,8 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="15"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="16"/>
@@ -838,8 +857,8 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="16"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="34"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
       <c r="N8" s="16"/>
@@ -866,8 +885,8 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="15"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="35"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="16"/>
@@ -894,8 +913,8 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="16"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="34"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="16"/>
@@ -922,8 +941,8 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="16"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="34"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
       <c r="N11" s="16"/>
@@ -950,8 +969,8 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="16"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="34"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
       <c r="N12" s="16"/>
@@ -978,8 +997,8 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="16"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="34"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
       <c r="N13" s="16"/>
@@ -1006,8 +1025,8 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="16"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="34"/>
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
       <c r="N14" s="16"/>
@@ -1034,8 +1053,8 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="16"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="34"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
       <c r="N15" s="16"/>
@@ -1062,8 +1081,8 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="16"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="34"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
       <c r="N16" s="16"/>
@@ -1090,8 +1109,8 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="16"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="34"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
       <c r="N17" s="16"/>
@@ -1118,8 +1137,8 @@
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="16"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="34"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
       <c r="N18" s="16"/>
@@ -1146,8 +1165,8 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="16"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="34"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
       <c r="N19" s="16"/>
@@ -1174,8 +1193,8 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="16"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="34"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="16"/>
@@ -1202,8 +1221,8 @@
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="16"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="34"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="16"/>
@@ -1230,8 +1249,8 @@
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="16"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="34"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="16"/>
@@ -1258,8 +1277,8 @@
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="16"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="34"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="16"/>
@@ -1286,8 +1305,8 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="16"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="34"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="16"/>
@@ -1314,8 +1333,8 @@
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="16"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="34"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="16"/>
@@ -1342,8 +1361,8 @@
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="16"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="34"/>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
       <c r="N26" s="16"/>
@@ -1370,8 +1389,8 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="16"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="34"/>
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
       <c r="N27" s="16"/>
@@ -1398,8 +1417,8 @@
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="16"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="34"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
       <c r="N28" s="16"/>
@@ -1426,8 +1445,8 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="16"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="34"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
       <c r="N29" s="16"/>
@@ -1454,8 +1473,8 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="16"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="34"/>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
       <c r="N30" s="16"/>
@@ -1482,8 +1501,8 @@
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="16"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="34"/>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
       <c r="N31" s="16"/>
@@ -1510,8 +1529,8 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="16"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="34"/>
       <c r="L32" s="13"/>
       <c r="M32" s="13"/>
       <c r="N32" s="16"/>
@@ -1538,8 +1557,8 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="16"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="34"/>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
       <c r="N33" s="16"/>
@@ -1566,8 +1585,8 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="16"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="34"/>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
       <c r="N34" s="16"/>
@@ -1594,8 +1613,8 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="16"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="34"/>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
       <c r="N35" s="16"/>
@@ -1622,8 +1641,8 @@
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="16"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="34"/>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
       <c r="N36" s="16"/>
@@ -1649,8 +1668,8 @@
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="16"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="34"/>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
       <c r="N37" s="16"/>
@@ -1677,8 +1696,8 @@
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="13"/>
@@ -1705,8 +1724,8 @@
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
       <c r="L39" s="13"/>
       <c r="M39" s="13"/>
       <c r="N39" s="13"/>
@@ -1733,8 +1752,8 @@
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
       <c r="L40" s="13"/>
       <c r="M40" s="13"/>
       <c r="N40" s="13"/>
@@ -1761,8 +1780,8 @@
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
       <c r="N41" s="13"/>
@@ -1789,8 +1808,8 @@
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
       <c r="L42" s="13"/>
       <c r="M42" s="13"/>
       <c r="N42" s="13"/>
@@ -1817,8 +1836,8 @@
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
       <c r="N43" s="13"/>
@@ -1845,8 +1864,8 @@
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
       <c r="N44" s="13"/>
@@ -1873,8 +1892,8 @@
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
       <c r="N45" s="13"/>
@@ -1901,8 +1920,8 @@
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
       <c r="L46" s="13"/>
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
@@ -1929,8 +1948,8 @@
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
       <c r="N47" s="13"/>
@@ -1957,8 +1976,8 @@
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
@@ -1985,8 +2004,8 @@
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
@@ -2013,8 +2032,8 @@
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
@@ -2041,8 +2060,8 @@
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
       <c r="N51" s="13"/>
@@ -2069,8 +2088,8 @@
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
@@ -2097,8 +2116,8 @@
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
       <c r="N53" s="13"/>
@@ -2125,8 +2144,8 @@
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
@@ -2153,8 +2172,8 @@
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
@@ -2181,8 +2200,8 @@
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
@@ -2209,8 +2228,8 @@
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
       <c r="N57" s="13"/>
@@ -2237,8 +2256,8 @@
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
       <c r="L58" s="13"/>
       <c r="M58" s="14"/>
       <c r="N58" s="14"/>
@@ -2265,8 +2284,8 @@
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
       <c r="N59" s="13"/>
@@ -2293,8 +2312,8 @@
       <c r="G60" s="13"/>
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
       <c r="N60" s="13"/>
@@ -2321,8 +2340,8 @@
       <c r="G61" s="13"/>
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
@@ -2349,8 +2368,8 @@
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
       <c r="N62" s="13"/>
@@ -2377,8 +2396,8 @@
       <c r="G63" s="13"/>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
@@ -2405,8 +2424,8 @@
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
@@ -2433,8 +2452,8 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -2461,8 +2480,8 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -2489,8 +2508,8 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -2517,8 +2536,8 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -2545,8 +2564,8 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -2573,8 +2592,8 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -2601,8 +2620,8 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -2629,8 +2648,8 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -2657,8 +2676,8 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -2685,8 +2704,8 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="32"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -2713,8 +2732,8 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -2741,8 +2760,8 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
+      <c r="J76" s="32"/>
+      <c r="K76" s="32"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -2769,8 +2788,8 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="32"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -2797,8 +2816,8 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
+      <c r="J78" s="32"/>
+      <c r="K78" s="32"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -2825,8 +2844,8 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="32"/>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -2853,8 +2872,8 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="32"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -2881,8 +2900,8 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
+      <c r="J81" s="32"/>
+      <c r="K81" s="32"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -2909,8 +2928,8 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
+      <c r="J82" s="32"/>
+      <c r="K82" s="32"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -2937,8 +2956,8 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="32"/>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -2965,8 +2984,8 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
+      <c r="J84" s="32"/>
+      <c r="K84" s="32"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -2993,8 +3012,8 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
+      <c r="J85" s="32"/>
+      <c r="K85" s="32"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -3021,8 +3040,8 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
+      <c r="J86" s="32"/>
+      <c r="K86" s="32"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -3049,8 +3068,8 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
+      <c r="J87" s="32"/>
+      <c r="K87" s="32"/>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -3077,8 +3096,8 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
+      <c r="J88" s="32"/>
+      <c r="K88" s="32"/>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -3105,8 +3124,8 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
+      <c r="J89" s="32"/>
+      <c r="K89" s="32"/>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -3133,8 +3152,8 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
+      <c r="J90" s="32"/>
+      <c r="K90" s="32"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -3161,8 +3180,8 @@
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
+      <c r="J91" s="32"/>
+      <c r="K91" s="32"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -3189,8 +3208,8 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
+      <c r="J92" s="32"/>
+      <c r="K92" s="32"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -3217,8 +3236,8 @@
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
+      <c r="J93" s="32"/>
+      <c r="K93" s="32"/>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -3245,8 +3264,8 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
+      <c r="J94" s="32"/>
+      <c r="K94" s="32"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -3273,8 +3292,8 @@
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
+      <c r="J95" s="32"/>
+      <c r="K95" s="32"/>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
@@ -3301,8 +3320,8 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
+      <c r="J96" s="32"/>
+      <c r="K96" s="32"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -3329,8 +3348,8 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
+      <c r="J97" s="32"/>
+      <c r="K97" s="32"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -3357,8 +3376,8 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
+      <c r="J98" s="32"/>
+      <c r="K98" s="32"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -3385,8 +3404,8 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
+      <c r="J99" s="32"/>
+      <c r="K99" s="32"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
@@ -3413,8 +3432,8 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
+      <c r="J100" s="32"/>
+      <c r="K100" s="32"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -3441,8 +3460,8 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
+      <c r="J101" s="32"/>
+      <c r="K101" s="32"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -3469,8 +3488,8 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
+      <c r="J102" s="32"/>
+      <c r="K102" s="32"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -3497,8 +3516,8 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
+      <c r="J103" s="32"/>
+      <c r="K103" s="32"/>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -3525,8 +3544,8 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
+      <c r="J104" s="32"/>
+      <c r="K104" s="32"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -3553,8 +3572,8 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
+      <c r="J105" s="32"/>
+      <c r="K105" s="32"/>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
@@ -3581,8 +3600,8 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
+      <c r="J106" s="32"/>
+      <c r="K106" s="32"/>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -3609,8 +3628,8 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
+      <c r="J107" s="32"/>
+      <c r="K107" s="32"/>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -3637,8 +3656,8 @@
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="2"/>
+      <c r="J108" s="32"/>
+      <c r="K108" s="32"/>
       <c r="L108" s="2"/>
       <c r="M108" s="4"/>
       <c r="N108" s="2"/>
@@ -3665,8 +3684,8 @@
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
+      <c r="J109" s="32"/>
+      <c r="K109" s="32"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
@@ -3693,8 +3712,8 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
+      <c r="J110" s="32"/>
+      <c r="K110" s="32"/>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -3721,8 +3740,8 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
+      <c r="J111" s="32"/>
+      <c r="K111" s="32"/>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
@@ -3749,8 +3768,8 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
+      <c r="J112" s="32"/>
+      <c r="K112" s="32"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -3777,8 +3796,8 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="1"/>
+      <c r="J113" s="32"/>
+      <c r="K113" s="33"/>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -3805,8 +3824,8 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
+      <c r="J114" s="32"/>
+      <c r="K114" s="32"/>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -3833,8 +3852,8 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
-      <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
+      <c r="J115" s="32"/>
+      <c r="K115" s="32"/>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -3861,8 +3880,8 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
+      <c r="J116" s="32"/>
+      <c r="K116" s="32"/>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
@@ -3889,8 +3908,8 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
+      <c r="J117" s="32"/>
+      <c r="K117" s="32"/>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
@@ -3917,8 +3936,8 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
+      <c r="J118" s="32"/>
+      <c r="K118" s="32"/>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
@@ -3945,8 +3964,8 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
-      <c r="J119" s="2"/>
-      <c r="K119" s="2"/>
+      <c r="J119" s="32"/>
+      <c r="K119" s="32"/>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -3973,8 +3992,8 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
-      <c r="J120" s="2"/>
-      <c r="K120" s="2"/>
+      <c r="J120" s="32"/>
+      <c r="K120" s="32"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -4001,8 +4020,8 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
+      <c r="J121" s="32"/>
+      <c r="K121" s="32"/>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
@@ -4029,8 +4048,8 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
+      <c r="J122" s="32"/>
+      <c r="K122" s="32"/>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -4057,8 +4076,8 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
+      <c r="J123" s="32"/>
+      <c r="K123" s="32"/>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -4085,8 +4104,8 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
+      <c r="J124" s="32"/>
+      <c r="K124" s="32"/>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -4113,8 +4132,8 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
+      <c r="J125" s="32"/>
+      <c r="K125" s="32"/>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -4141,8 +4160,8 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
-      <c r="J126" s="2"/>
-      <c r="K126" s="2"/>
+      <c r="J126" s="32"/>
+      <c r="K126" s="32"/>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -4169,8 +4188,8 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
+      <c r="J127" s="32"/>
+      <c r="K127" s="32"/>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -4197,8 +4216,8 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2"/>
+      <c r="J128" s="32"/>
+      <c r="K128" s="32"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -4225,8 +4244,8 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
+      <c r="J129" s="32"/>
+      <c r="K129" s="32"/>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
@@ -4253,8 +4272,8 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
+      <c r="J130" s="32"/>
+      <c r="K130" s="32"/>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
@@ -4281,8 +4300,8 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
+      <c r="J131" s="32"/>
+      <c r="K131" s="32"/>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -4309,8 +4328,8 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
+      <c r="J132" s="32"/>
+      <c r="K132" s="32"/>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -4337,8 +4356,8 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
-      <c r="J133" s="2"/>
-      <c r="K133" s="2"/>
+      <c r="J133" s="32"/>
+      <c r="K133" s="32"/>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
@@ -4365,8 +4384,8 @@
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
+      <c r="J134" s="33"/>
+      <c r="K134" s="33"/>
       <c r="L134" s="2"/>
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
@@ -4393,8 +4412,8 @@
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
-      <c r="J135" s="1"/>
-      <c r="K135" s="1"/>
+      <c r="J135" s="33"/>
+      <c r="K135" s="33"/>
       <c r="L135" s="2"/>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
@@ -4421,8 +4440,8 @@
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
-      <c r="K136" s="1"/>
+      <c r="J136" s="33"/>
+      <c r="K136" s="33"/>
       <c r="L136" s="2"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
@@ -4449,8 +4468,8 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
+      <c r="J137" s="33"/>
+      <c r="K137" s="33"/>
       <c r="L137" s="2"/>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
@@ -4477,8 +4496,8 @@
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="1"/>
-      <c r="K138" s="1"/>
+      <c r="J138" s="33"/>
+      <c r="K138" s="33"/>
       <c r="L138" s="2"/>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
@@ -4505,8 +4524,8 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
-      <c r="K139" s="1"/>
+      <c r="J139" s="33"/>
+      <c r="K139" s="33"/>
       <c r="L139" s="2"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
@@ -4533,8 +4552,8 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
-      <c r="K140" s="1"/>
+      <c r="J140" s="33"/>
+      <c r="K140" s="33"/>
       <c r="L140" s="2"/>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
@@ -4561,8 +4580,8 @@
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
-      <c r="J141" s="1"/>
-      <c r="K141" s="1"/>
+      <c r="J141" s="33"/>
+      <c r="K141" s="33"/>
       <c r="L141" s="2"/>
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
@@ -4589,8 +4608,8 @@
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
-      <c r="J142" s="1"/>
-      <c r="K142" s="1"/>
+      <c r="J142" s="33"/>
+      <c r="K142" s="33"/>
       <c r="L142" s="2"/>
       <c r="M142" s="1"/>
       <c r="N142" s="1"/>
@@ -4617,8 +4636,8 @@
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
-      <c r="J143" s="1"/>
-      <c r="K143" s="1"/>
+      <c r="J143" s="33"/>
+      <c r="K143" s="33"/>
       <c r="L143" s="2"/>
       <c r="M143" s="1"/>
       <c r="N143" s="1"/>
@@ -4645,8 +4664,8 @@
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
-      <c r="J144" s="1"/>
-      <c r="K144" s="1"/>
+      <c r="J144" s="33"/>
+      <c r="K144" s="33"/>
       <c r="L144" s="2"/>
       <c r="M144" s="1"/>
       <c r="N144" s="1"/>
@@ -4673,8 +4692,8 @@
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
-      <c r="J145" s="1"/>
-      <c r="K145" s="1"/>
+      <c r="J145" s="33"/>
+      <c r="K145" s="33"/>
       <c r="L145" s="2"/>
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
@@ -4701,8 +4720,8 @@
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
-      <c r="J146" s="1"/>
-      <c r="K146" s="1"/>
+      <c r="J146" s="33"/>
+      <c r="K146" s="33"/>
       <c r="L146" s="2"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
@@ -4729,8 +4748,8 @@
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
-      <c r="J147" s="1"/>
-      <c r="K147" s="1"/>
+      <c r="J147" s="33"/>
+      <c r="K147" s="33"/>
       <c r="L147" s="2"/>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
@@ -4757,8 +4776,8 @@
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
-      <c r="J148" s="1"/>
-      <c r="K148" s="1"/>
+      <c r="J148" s="33"/>
+      <c r="K148" s="33"/>
       <c r="L148" s="2"/>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
@@ -4785,8 +4804,8 @@
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
-      <c r="J149" s="1"/>
-      <c r="K149" s="1"/>
+      <c r="J149" s="33"/>
+      <c r="K149" s="33"/>
       <c r="L149" s="2"/>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
@@ -4813,8 +4832,8 @@
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
-      <c r="K150" s="1"/>
+      <c r="J150" s="33"/>
+      <c r="K150" s="33"/>
       <c r="L150" s="2"/>
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
@@ -4841,8 +4860,8 @@
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
-      <c r="J151" s="1"/>
-      <c r="K151" s="1"/>
+      <c r="J151" s="33"/>
+      <c r="K151" s="33"/>
       <c r="L151" s="2"/>
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
@@ -4869,8 +4888,8 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
-      <c r="J152" s="1"/>
-      <c r="K152" s="1"/>
+      <c r="J152" s="33"/>
+      <c r="K152" s="33"/>
       <c r="L152" s="2"/>
       <c r="M152" s="1"/>
       <c r="N152" s="1"/>
@@ -4897,8 +4916,8 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
-      <c r="J153" s="1"/>
-      <c r="K153" s="1"/>
+      <c r="J153" s="33"/>
+      <c r="K153" s="33"/>
       <c r="L153" s="2"/>
       <c r="M153" s="1"/>
       <c r="N153" s="1"/>
@@ -4925,8 +4944,8 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
-      <c r="J154" s="1"/>
-      <c r="K154" s="1"/>
+      <c r="J154" s="33"/>
+      <c r="K154" s="33"/>
       <c r="L154" s="2"/>
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
@@ -4953,8 +4972,8 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
-      <c r="J155" s="1"/>
-      <c r="K155" s="1"/>
+      <c r="J155" s="33"/>
+      <c r="K155" s="33"/>
       <c r="L155" s="2"/>
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
@@ -4981,8 +5000,8 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
-      <c r="J156" s="1"/>
-      <c r="K156" s="1"/>
+      <c r="J156" s="33"/>
+      <c r="K156" s="33"/>
       <c r="L156" s="2"/>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -5009,8 +5028,8 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
-      <c r="J157" s="1"/>
-      <c r="K157" s="1"/>
+      <c r="J157" s="33"/>
+      <c r="K157" s="33"/>
       <c r="L157" s="2"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -5037,8 +5056,8 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
-      <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
+      <c r="J158" s="33"/>
+      <c r="K158" s="33"/>
       <c r="L158" s="2"/>
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
@@ -5065,8 +5084,8 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
+      <c r="J159" s="33"/>
+      <c r="K159" s="33"/>
       <c r="L159" s="2"/>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -5093,8 +5112,8 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
-      <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
+      <c r="J160" s="33"/>
+      <c r="K160" s="33"/>
       <c r="L160" s="2"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
@@ -5121,8 +5140,8 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
-      <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
+      <c r="J161" s="33"/>
+      <c r="K161" s="33"/>
       <c r="L161" s="2"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
@@ -5149,8 +5168,8 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
-      <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
+      <c r="J162" s="33"/>
+      <c r="K162" s="33"/>
       <c r="L162" s="2"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
@@ -5177,8 +5196,8 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
-      <c r="J163" s="1"/>
-      <c r="K163" s="1"/>
+      <c r="J163" s="33"/>
+      <c r="K163" s="33"/>
       <c r="L163" s="2"/>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
@@ -5205,8 +5224,8 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
-      <c r="J164" s="1"/>
-      <c r="K164" s="1"/>
+      <c r="J164" s="33"/>
+      <c r="K164" s="33"/>
       <c r="L164" s="2"/>
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
@@ -5233,8 +5252,8 @@
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
-      <c r="J165" s="1"/>
-      <c r="K165" s="1"/>
+      <c r="J165" s="33"/>
+      <c r="K165" s="33"/>
       <c r="L165" s="2"/>
       <c r="M165" s="1"/>
       <c r="N165" s="1"/>
@@ -5261,8 +5280,8 @@
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
-      <c r="J166" s="1"/>
-      <c r="K166" s="1"/>
+      <c r="J166" s="33"/>
+      <c r="K166" s="33"/>
       <c r="L166" s="2"/>
       <c r="M166" s="1"/>
       <c r="N166" s="1"/>
@@ -5289,8 +5308,8 @@
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
-      <c r="J167" s="1"/>
-      <c r="K167" s="1"/>
+      <c r="J167" s="33"/>
+      <c r="K167" s="33"/>
       <c r="L167" s="2"/>
       <c r="M167" s="1"/>
       <c r="N167" s="1"/>
@@ -5317,8 +5336,8 @@
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
-      <c r="J168" s="1"/>
-      <c r="K168" s="1"/>
+      <c r="J168" s="33"/>
+      <c r="K168" s="33"/>
       <c r="L168" s="2"/>
       <c r="M168" s="1"/>
       <c r="N168" s="1"/>
@@ -5345,8 +5364,8 @@
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
-      <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
+      <c r="J169" s="33"/>
+      <c r="K169" s="33"/>
       <c r="L169" s="2"/>
       <c r="M169" s="1"/>
       <c r="N169" s="1"/>
@@ -5373,8 +5392,8 @@
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
-      <c r="J170" s="1"/>
-      <c r="K170" s="1"/>
+      <c r="J170" s="33"/>
+      <c r="K170" s="33"/>
       <c r="L170" s="2"/>
       <c r="M170" s="1"/>
       <c r="N170" s="1"/>
@@ -5401,8 +5420,8 @@
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
-      <c r="J171" s="1"/>
-      <c r="K171" s="1"/>
+      <c r="J171" s="33"/>
+      <c r="K171" s="33"/>
       <c r="L171" s="2"/>
       <c r="M171" s="1"/>
       <c r="N171" s="1"/>
@@ -5429,8 +5448,8 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
-      <c r="J172" s="1"/>
-      <c r="K172" s="1"/>
+      <c r="J172" s="33"/>
+      <c r="K172" s="33"/>
       <c r="L172" s="2"/>
       <c r="M172" s="1"/>
       <c r="N172" s="1"/>
@@ -5457,8 +5476,8 @@
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
-      <c r="J173" s="1"/>
-      <c r="K173" s="1"/>
+      <c r="J173" s="33"/>
+      <c r="K173" s="33"/>
       <c r="L173" s="2"/>
       <c r="M173" s="1"/>
       <c r="N173" s="1"/>
@@ -5485,8 +5504,8 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
-      <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
+      <c r="J174" s="33"/>
+      <c r="K174" s="33"/>
       <c r="L174" s="2"/>
       <c r="M174" s="1"/>
       <c r="N174" s="1"/>
@@ -5513,8 +5532,8 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
-      <c r="J175" s="1"/>
-      <c r="K175" s="1"/>
+      <c r="J175" s="33"/>
+      <c r="K175" s="33"/>
       <c r="L175" s="2"/>
       <c r="M175" s="1"/>
       <c r="N175" s="1"/>
@@ -5541,8 +5560,8 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
-      <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
+      <c r="J176" s="33"/>
+      <c r="K176" s="33"/>
       <c r="L176" s="2"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
@@ -5569,8 +5588,8 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
-      <c r="J177" s="1"/>
-      <c r="K177" s="1"/>
+      <c r="J177" s="33"/>
+      <c r="K177" s="33"/>
       <c r="L177" s="2"/>
       <c r="M177" s="1"/>
       <c r="N177" s="1"/>
@@ -5597,8 +5616,8 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
+      <c r="J178" s="33"/>
+      <c r="K178" s="33"/>
       <c r="L178" s="2"/>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
@@ -5625,8 +5644,8 @@
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
-      <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
+      <c r="J179" s="33"/>
+      <c r="K179" s="33"/>
       <c r="L179" s="2"/>
       <c r="M179" s="1"/>
       <c r="N179" s="1"/>
@@ -5653,8 +5672,8 @@
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
-      <c r="J180" s="1"/>
-      <c r="K180" s="1"/>
+      <c r="J180" s="33"/>
+      <c r="K180" s="33"/>
       <c r="L180" s="2"/>
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
@@ -5681,8 +5700,8 @@
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
-      <c r="J181" s="1"/>
-      <c r="K181" s="1"/>
+      <c r="J181" s="33"/>
+      <c r="K181" s="33"/>
       <c r="L181" s="2"/>
       <c r="M181" s="1"/>
       <c r="N181" s="1"/>
@@ -5709,8 +5728,8 @@
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
-      <c r="J182" s="1"/>
-      <c r="K182" s="1"/>
+      <c r="J182" s="33"/>
+      <c r="K182" s="33"/>
       <c r="L182" s="2"/>
       <c r="M182" s="1"/>
       <c r="N182" s="1"/>
@@ -5737,8 +5756,8 @@
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
-      <c r="J183" s="1"/>
-      <c r="K183" s="1"/>
+      <c r="J183" s="33"/>
+      <c r="K183" s="33"/>
       <c r="L183" s="2"/>
       <c r="M183" s="1"/>
       <c r="N183" s="1"/>
@@ -5765,8 +5784,8 @@
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
-      <c r="J184" s="1"/>
-      <c r="K184" s="1"/>
+      <c r="J184" s="33"/>
+      <c r="K184" s="33"/>
       <c r="L184" s="2"/>
       <c r="M184" s="1"/>
       <c r="N184" s="1"/>
@@ -5793,8 +5812,8 @@
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
-      <c r="J185" s="1"/>
-      <c r="K185" s="1"/>
+      <c r="J185" s="33"/>
+      <c r="K185" s="33"/>
       <c r="L185" s="2"/>
       <c r="M185" s="1"/>
       <c r="N185" s="1"/>
@@ -5821,8 +5840,8 @@
       <c r="G186" s="1"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
-      <c r="J186" s="1"/>
-      <c r="K186" s="1"/>
+      <c r="J186" s="33"/>
+      <c r="K186" s="33"/>
       <c r="L186" s="2"/>
       <c r="M186" s="1"/>
       <c r="N186" s="1"/>
@@ -5849,8 +5868,8 @@
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
-      <c r="J187" s="1"/>
-      <c r="K187" s="1"/>
+      <c r="J187" s="33"/>
+      <c r="K187" s="33"/>
       <c r="L187" s="2"/>
       <c r="M187" s="1"/>
       <c r="N187" s="1"/>
@@ -5877,8 +5896,8 @@
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
-      <c r="J188" s="1"/>
-      <c r="K188" s="1"/>
+      <c r="J188" s="33"/>
+      <c r="K188" s="33"/>
       <c r="L188" s="2"/>
       <c r="M188" s="1"/>
       <c r="N188" s="1"/>
@@ -5905,8 +5924,8 @@
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
-      <c r="J189" s="1"/>
-      <c r="K189" s="1"/>
+      <c r="J189" s="33"/>
+      <c r="K189" s="33"/>
       <c r="L189" s="2"/>
       <c r="M189" s="1"/>
       <c r="N189" s="1"/>
@@ -5933,8 +5952,8 @@
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
-      <c r="J190" s="1"/>
-      <c r="K190" s="1"/>
+      <c r="J190" s="33"/>
+      <c r="K190" s="33"/>
       <c r="L190" s="2"/>
       <c r="M190" s="1"/>
       <c r="N190" s="1"/>
@@ -5961,8 +5980,8 @@
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
-      <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
+      <c r="J191" s="33"/>
+      <c r="K191" s="33"/>
       <c r="L191" s="2"/>
       <c r="M191" s="1"/>
       <c r="N191" s="1"/>
@@ -5989,8 +6008,8 @@
       <c r="G192" s="1"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
-      <c r="J192" s="1"/>
-      <c r="K192" s="1"/>
+      <c r="J192" s="33"/>
+      <c r="K192" s="33"/>
       <c r="L192" s="2"/>
       <c r="M192" s="1"/>
       <c r="N192" s="1"/>
@@ -6017,8 +6036,8 @@
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
-      <c r="J193" s="1"/>
-      <c r="K193" s="1"/>
+      <c r="J193" s="33"/>
+      <c r="K193" s="33"/>
       <c r="L193" s="2"/>
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
@@ -6045,8 +6064,8 @@
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
-      <c r="J194" s="1"/>
-      <c r="K194" s="1"/>
+      <c r="J194" s="33"/>
+      <c r="K194" s="33"/>
       <c r="L194" s="2"/>
       <c r="M194" s="1"/>
       <c r="N194" s="1"/>
@@ -6073,8 +6092,8 @@
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
-      <c r="J195" s="1"/>
-      <c r="K195" s="1"/>
+      <c r="J195" s="33"/>
+      <c r="K195" s="33"/>
       <c r="L195" s="2"/>
       <c r="M195" s="1"/>
       <c r="N195" s="1"/>
@@ -6101,8 +6120,8 @@
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
-      <c r="J196" s="1"/>
-      <c r="K196" s="1"/>
+      <c r="J196" s="33"/>
+      <c r="K196" s="33"/>
       <c r="L196" s="2"/>
       <c r="M196" s="1"/>
       <c r="N196" s="1"/>
@@ -6129,8 +6148,8 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
-      <c r="J197" s="1"/>
-      <c r="K197" s="1"/>
+      <c r="J197" s="33"/>
+      <c r="K197" s="33"/>
       <c r="L197" s="2"/>
       <c r="M197" s="1"/>
       <c r="N197" s="1"/>
@@ -6157,8 +6176,8 @@
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
-      <c r="J198" s="1"/>
-      <c r="K198" s="1"/>
+      <c r="J198" s="33"/>
+      <c r="K198" s="33"/>
       <c r="L198" s="2"/>
       <c r="M198" s="1"/>
       <c r="N198" s="1"/>
@@ -6185,8 +6204,8 @@
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
-      <c r="J199" s="1"/>
-      <c r="K199" s="1"/>
+      <c r="J199" s="33"/>
+      <c r="K199" s="33"/>
       <c r="L199" s="2"/>
       <c r="M199" s="1"/>
       <c r="N199" s="1"/>
@@ -6213,8 +6232,8 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
-      <c r="J200" s="1"/>
-      <c r="K200" s="1"/>
+      <c r="J200" s="33"/>
+      <c r="K200" s="33"/>
       <c r="L200" s="2"/>
       <c r="M200" s="1"/>
       <c r="N200" s="1"/>
@@ -6241,8 +6260,8 @@
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
       <c r="I201" s="1"/>
-      <c r="J201" s="1"/>
-      <c r="K201" s="1"/>
+      <c r="J201" s="33"/>
+      <c r="K201" s="33"/>
       <c r="L201" s="2"/>
       <c r="M201" s="1"/>
       <c r="N201" s="1"/>
@@ -6269,8 +6288,8 @@
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
       <c r="I202" s="1"/>
-      <c r="J202" s="1"/>
-      <c r="K202" s="1"/>
+      <c r="J202" s="33"/>
+      <c r="K202" s="33"/>
       <c r="L202" s="2"/>
       <c r="M202" s="1"/>
       <c r="N202" s="1"/>
@@ -6297,8 +6316,8 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
       <c r="I203" s="1"/>
-      <c r="J203" s="1"/>
-      <c r="K203" s="1"/>
+      <c r="J203" s="33"/>
+      <c r="K203" s="33"/>
       <c r="L203" s="2"/>
       <c r="M203" s="1"/>
       <c r="N203" s="1"/>
@@ -6325,8 +6344,8 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
       <c r="I204" s="1"/>
-      <c r="J204" s="1"/>
-      <c r="K204" s="1"/>
+      <c r="J204" s="33"/>
+      <c r="K204" s="33"/>
       <c r="L204" s="2"/>
       <c r="M204" s="1"/>
       <c r="N204" s="1"/>
@@ -6353,8 +6372,8 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
-      <c r="J205" s="1"/>
-      <c r="K205" s="1"/>
+      <c r="J205" s="33"/>
+      <c r="K205" s="33"/>
       <c r="L205" s="2"/>
       <c r="M205" s="1"/>
       <c r="N205" s="1"/>
@@ -6381,8 +6400,8 @@
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
-      <c r="J206" s="1"/>
-      <c r="K206" s="1"/>
+      <c r="J206" s="33"/>
+      <c r="K206" s="33"/>
       <c r="L206" s="2"/>
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
@@ -6409,8 +6428,8 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
-      <c r="J207" s="1"/>
-      <c r="K207" s="1"/>
+      <c r="J207" s="33"/>
+      <c r="K207" s="33"/>
       <c r="L207" s="2"/>
       <c r="M207" s="1"/>
       <c r="N207" s="1"/>
@@ -6437,8 +6456,8 @@
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
-      <c r="J208" s="1"/>
-      <c r="K208" s="1"/>
+      <c r="J208" s="33"/>
+      <c r="K208" s="33"/>
       <c r="L208" s="2"/>
       <c r="M208" s="1"/>
       <c r="N208" s="1"/>
@@ -6465,8 +6484,8 @@
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
-      <c r="J209" s="1"/>
-      <c r="K209" s="1"/>
+      <c r="J209" s="33"/>
+      <c r="K209" s="33"/>
       <c r="L209" s="2"/>
       <c r="M209" s="1"/>
       <c r="N209" s="1"/>
@@ -6493,8 +6512,8 @@
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
-      <c r="J210" s="1"/>
-      <c r="K210" s="1"/>
+      <c r="J210" s="33"/>
+      <c r="K210" s="33"/>
       <c r="L210" s="2"/>
       <c r="M210" s="1"/>
       <c r="N210" s="1"/>
@@ -6521,8 +6540,8 @@
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
-      <c r="J211" s="1"/>
-      <c r="K211" s="1"/>
+      <c r="J211" s="33"/>
+      <c r="K211" s="33"/>
       <c r="L211" s="2"/>
       <c r="M211" s="1"/>
       <c r="N211" s="1"/>
@@ -6549,8 +6568,8 @@
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
-      <c r="J212" s="1"/>
-      <c r="K212" s="1"/>
+      <c r="J212" s="33"/>
+      <c r="K212" s="33"/>
       <c r="L212" s="2"/>
       <c r="M212" s="1"/>
       <c r="N212" s="1"/>
@@ -6577,8 +6596,8 @@
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
-      <c r="J213" s="1"/>
-      <c r="K213" s="1"/>
+      <c r="J213" s="33"/>
+      <c r="K213" s="33"/>
       <c r="L213" s="2"/>
       <c r="M213" s="1"/>
       <c r="N213" s="1"/>
@@ -6605,8 +6624,8 @@
       <c r="G214" s="1"/>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
-      <c r="J214" s="1"/>
-      <c r="K214" s="1"/>
+      <c r="J214" s="33"/>
+      <c r="K214" s="33"/>
       <c r="L214" s="2"/>
       <c r="M214" s="1"/>
       <c r="N214" s="1"/>
@@ -6633,8 +6652,8 @@
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
-      <c r="J215" s="1"/>
-      <c r="K215" s="1"/>
+      <c r="J215" s="33"/>
+      <c r="K215" s="33"/>
       <c r="L215" s="2"/>
       <c r="M215" s="1"/>
       <c r="N215" s="1"/>
@@ -6661,8 +6680,8 @@
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
       <c r="I216" s="1"/>
-      <c r="J216" s="1"/>
-      <c r="K216" s="1"/>
+      <c r="J216" s="33"/>
+      <c r="K216" s="33"/>
       <c r="L216" s="2"/>
       <c r="M216" s="1"/>
       <c r="N216" s="1"/>
@@ -6689,8 +6708,8 @@
       <c r="G217" s="1"/>
       <c r="H217" s="1"/>
       <c r="I217" s="1"/>
-      <c r="J217" s="1"/>
-      <c r="K217" s="1"/>
+      <c r="J217" s="33"/>
+      <c r="K217" s="33"/>
       <c r="L217" s="2"/>
       <c r="M217" s="1"/>
       <c r="N217" s="1"/>
@@ -6717,8 +6736,8 @@
       <c r="G218" s="1"/>
       <c r="H218" s="1"/>
       <c r="I218" s="1"/>
-      <c r="J218" s="1"/>
-      <c r="K218" s="1"/>
+      <c r="J218" s="33"/>
+      <c r="K218" s="33"/>
       <c r="L218" s="2"/>
       <c r="M218" s="1"/>
       <c r="N218" s="1"/>
@@ -6745,8 +6764,8 @@
       <c r="G219" s="1"/>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
-      <c r="J219" s="1"/>
-      <c r="K219" s="1"/>
+      <c r="J219" s="33"/>
+      <c r="K219" s="33"/>
       <c r="L219" s="2"/>
       <c r="M219" s="1"/>
       <c r="N219" s="1"/>
@@ -6773,8 +6792,8 @@
       <c r="G220" s="1"/>
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
-      <c r="J220" s="1"/>
-      <c r="K220" s="1"/>
+      <c r="J220" s="33"/>
+      <c r="K220" s="33"/>
       <c r="L220" s="2"/>
       <c r="M220" s="1"/>
       <c r="N220" s="1"/>
@@ -6801,8 +6820,8 @@
       <c r="G221" s="1"/>
       <c r="H221" s="1"/>
       <c r="I221" s="1"/>
-      <c r="J221" s="1"/>
-      <c r="K221" s="1"/>
+      <c r="J221" s="33"/>
+      <c r="K221" s="33"/>
       <c r="L221" s="2"/>
       <c r="M221" s="1"/>
       <c r="N221" s="1"/>
@@ -6829,8 +6848,8 @@
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
       <c r="I222" s="1"/>
-      <c r="J222" s="1"/>
-      <c r="K222" s="1"/>
+      <c r="J222" s="33"/>
+      <c r="K222" s="33"/>
       <c r="L222" s="2"/>
       <c r="M222" s="1"/>
       <c r="N222" s="1"/>
@@ -6857,8 +6876,8 @@
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
       <c r="I223" s="1"/>
-      <c r="J223" s="1"/>
-      <c r="K223" s="1"/>
+      <c r="J223" s="33"/>
+      <c r="K223" s="33"/>
       <c r="L223" s="2"/>
       <c r="M223" s="1"/>
       <c r="N223" s="1"/>
@@ -6885,8 +6904,8 @@
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
       <c r="I224" s="1"/>
-      <c r="J224" s="1"/>
-      <c r="K224" s="1"/>
+      <c r="J224" s="33"/>
+      <c r="K224" s="33"/>
       <c r="L224" s="2"/>
       <c r="M224" s="1"/>
       <c r="N224" s="1"/>
@@ -6913,8 +6932,8 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
       <c r="I225" s="1"/>
-      <c r="J225" s="1"/>
-      <c r="K225" s="1"/>
+      <c r="J225" s="33"/>
+      <c r="K225" s="33"/>
       <c r="L225" s="2"/>
       <c r="M225" s="1"/>
       <c r="N225" s="1"/>
@@ -6941,8 +6960,8 @@
       <c r="G226" s="1"/>
       <c r="H226" s="1"/>
       <c r="I226" s="1"/>
-      <c r="J226" s="1"/>
-      <c r="K226" s="1"/>
+      <c r="J226" s="33"/>
+      <c r="K226" s="33"/>
       <c r="L226" s="2"/>
       <c r="M226" s="1"/>
       <c r="N226" s="1"/>
@@ -6969,8 +6988,8 @@
       <c r="G227" s="1"/>
       <c r="H227" s="1"/>
       <c r="I227" s="1"/>
-      <c r="J227" s="1"/>
-      <c r="K227" s="1"/>
+      <c r="J227" s="33"/>
+      <c r="K227" s="33"/>
       <c r="L227" s="2"/>
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
@@ -6997,8 +7016,8 @@
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
       <c r="I228" s="1"/>
-      <c r="J228" s="1"/>
-      <c r="K228" s="1"/>
+      <c r="J228" s="33"/>
+      <c r="K228" s="33"/>
       <c r="L228" s="2"/>
       <c r="M228" s="1"/>
       <c r="N228" s="1"/>
@@ -7025,8 +7044,8 @@
       <c r="G229" s="1"/>
       <c r="H229" s="1"/>
       <c r="I229" s="1"/>
-      <c r="J229" s="1"/>
-      <c r="K229" s="1"/>
+      <c r="J229" s="33"/>
+      <c r="K229" s="33"/>
       <c r="L229" s="2"/>
       <c r="M229" s="1"/>
       <c r="N229" s="1"/>
@@ -7053,8 +7072,8 @@
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
       <c r="I230" s="1"/>
-      <c r="J230" s="1"/>
-      <c r="K230" s="1"/>
+      <c r="J230" s="33"/>
+      <c r="K230" s="33"/>
       <c r="L230" s="2"/>
       <c r="M230" s="1"/>
       <c r="N230" s="1"/>
@@ -7081,8 +7100,8 @@
       <c r="G231" s="1"/>
       <c r="H231" s="1"/>
       <c r="I231" s="1"/>
-      <c r="J231" s="1"/>
-      <c r="K231" s="1"/>
+      <c r="J231" s="33"/>
+      <c r="K231" s="33"/>
       <c r="L231" s="2"/>
       <c r="M231" s="1"/>
       <c r="N231" s="1"/>
@@ -7109,8 +7128,8 @@
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
       <c r="I232" s="1"/>
-      <c r="J232" s="1"/>
-      <c r="K232" s="1"/>
+      <c r="J232" s="33"/>
+      <c r="K232" s="33"/>
       <c r="L232" s="2"/>
       <c r="M232" s="1"/>
       <c r="N232" s="1"/>
@@ -7137,8 +7156,8 @@
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
       <c r="I233" s="1"/>
-      <c r="J233" s="1"/>
-      <c r="K233" s="1"/>
+      <c r="J233" s="33"/>
+      <c r="K233" s="33"/>
       <c r="L233" s="2"/>
       <c r="M233" s="1"/>
       <c r="N233" s="1"/>
@@ -7165,8 +7184,8 @@
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
-      <c r="J234" s="1"/>
-      <c r="K234" s="1"/>
+      <c r="J234" s="33"/>
+      <c r="K234" s="33"/>
       <c r="L234" s="2"/>
       <c r="M234" s="1"/>
       <c r="N234" s="1"/>
@@ -7193,8 +7212,8 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
-      <c r="J235" s="1"/>
-      <c r="K235" s="1"/>
+      <c r="J235" s="33"/>
+      <c r="K235" s="33"/>
       <c r="L235" s="2"/>
       <c r="M235" s="1"/>
       <c r="N235" s="1"/>
@@ -7221,8 +7240,8 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
-      <c r="J236" s="1"/>
-      <c r="K236" s="1"/>
+      <c r="J236" s="33"/>
+      <c r="K236" s="33"/>
       <c r="L236" s="2"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
@@ -7249,8 +7268,8 @@
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
-      <c r="J237" s="1"/>
-      <c r="K237" s="1"/>
+      <c r="J237" s="33"/>
+      <c r="K237" s="33"/>
       <c r="L237" s="2"/>
       <c r="M237" s="1"/>
       <c r="N237" s="1"/>
@@ -7277,8 +7296,8 @@
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
-      <c r="J238" s="1"/>
-      <c r="K238" s="1"/>
+      <c r="J238" s="33"/>
+      <c r="K238" s="33"/>
       <c r="L238" s="2"/>
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
@@ -7305,8 +7324,8 @@
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
-      <c r="J239" s="1"/>
-      <c r="K239" s="1"/>
+      <c r="J239" s="33"/>
+      <c r="K239" s="33"/>
       <c r="L239" s="2"/>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
@@ -7333,8 +7352,8 @@
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
-      <c r="J240" s="1"/>
-      <c r="K240" s="1"/>
+      <c r="J240" s="33"/>
+      <c r="K240" s="33"/>
       <c r="L240" s="2"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
@@ -7361,8 +7380,8 @@
       <c r="G241" s="1"/>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
-      <c r="J241" s="1"/>
-      <c r="K241" s="1"/>
+      <c r="J241" s="33"/>
+      <c r="K241" s="33"/>
       <c r="L241" s="2"/>
       <c r="M241" s="1"/>
       <c r="N241" s="1"/>
@@ -7389,8 +7408,8 @@
       <c r="G242" s="1"/>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
-      <c r="J242" s="1"/>
-      <c r="K242" s="1"/>
+      <c r="J242" s="33"/>
+      <c r="K242" s="33"/>
       <c r="L242" s="2"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
@@ -7417,8 +7436,8 @@
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
-      <c r="J243" s="1"/>
-      <c r="K243" s="1"/>
+      <c r="J243" s="33"/>
+      <c r="K243" s="33"/>
       <c r="L243" s="2"/>
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
@@ -7445,8 +7464,8 @@
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
-      <c r="J244" s="1"/>
-      <c r="K244" s="1"/>
+      <c r="J244" s="33"/>
+      <c r="K244" s="33"/>
       <c r="L244" s="2"/>
       <c r="M244" s="1"/>
       <c r="N244" s="1"/>
@@ -7473,8 +7492,8 @@
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
-      <c r="J245" s="1"/>
-      <c r="K245" s="1"/>
+      <c r="J245" s="33"/>
+      <c r="K245" s="33"/>
       <c r="L245" s="2"/>
       <c r="M245" s="1"/>
       <c r="N245" s="1"/>
@@ -7501,8 +7520,8 @@
       <c r="G246" s="1"/>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
-      <c r="J246" s="1"/>
-      <c r="K246" s="1"/>
+      <c r="J246" s="33"/>
+      <c r="K246" s="33"/>
       <c r="L246" s="2"/>
       <c r="M246" s="1"/>
       <c r="N246" s="1"/>
@@ -7529,8 +7548,8 @@
       <c r="G247" s="1"/>
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
-      <c r="J247" s="1"/>
-      <c r="K247" s="1"/>
+      <c r="J247" s="33"/>
+      <c r="K247" s="33"/>
       <c r="L247" s="2"/>
       <c r="M247" s="1"/>
       <c r="N247" s="1"/>
@@ -7557,8 +7576,8 @@
       <c r="G248" s="1"/>
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
-      <c r="J248" s="1"/>
-      <c r="K248" s="1"/>
+      <c r="J248" s="33"/>
+      <c r="K248" s="33"/>
       <c r="L248" s="2"/>
       <c r="M248" s="1"/>
       <c r="N248" s="1"/>
@@ -7585,8 +7604,8 @@
       <c r="G249" s="1"/>
       <c r="H249" s="1"/>
       <c r="I249" s="1"/>
-      <c r="J249" s="1"/>
-      <c r="K249" s="1"/>
+      <c r="J249" s="33"/>
+      <c r="K249" s="33"/>
       <c r="L249" s="2"/>
       <c r="M249" s="1"/>
       <c r="N249" s="1"/>
@@ -7613,8 +7632,8 @@
       <c r="G250" s="1"/>
       <c r="H250" s="1"/>
       <c r="I250" s="1"/>
-      <c r="J250" s="1"/>
-      <c r="K250" s="1"/>
+      <c r="J250" s="33"/>
+      <c r="K250" s="33"/>
       <c r="L250" s="2"/>
       <c r="M250" s="1"/>
       <c r="N250" s="1"/>
@@ -7641,8 +7660,8 @@
       <c r="G251" s="1"/>
       <c r="H251" s="1"/>
       <c r="I251" s="1"/>
-      <c r="J251" s="1"/>
-      <c r="K251" s="1"/>
+      <c r="J251" s="33"/>
+      <c r="K251" s="33"/>
       <c r="L251" s="2"/>
       <c r="M251" s="1"/>
       <c r="N251" s="1"/>
@@ -7669,8 +7688,8 @@
       <c r="G252" s="1"/>
       <c r="H252" s="1"/>
       <c r="I252" s="1"/>
-      <c r="J252" s="1"/>
-      <c r="K252" s="1"/>
+      <c r="J252" s="33"/>
+      <c r="K252" s="33"/>
       <c r="L252" s="2"/>
       <c r="M252" s="1"/>
       <c r="N252" s="1"/>
@@ -7697,8 +7716,8 @@
       <c r="G253" s="1"/>
       <c r="H253" s="1"/>
       <c r="I253" s="1"/>
-      <c r="J253" s="1"/>
-      <c r="K253" s="1"/>
+      <c r="J253" s="33"/>
+      <c r="K253" s="33"/>
       <c r="L253" s="2"/>
       <c r="M253" s="1"/>
       <c r="N253" s="1"/>
@@ -7725,8 +7744,8 @@
       <c r="G254" s="1"/>
       <c r="H254" s="1"/>
       <c r="I254" s="1"/>
-      <c r="J254" s="1"/>
-      <c r="K254" s="1"/>
+      <c r="J254" s="33"/>
+      <c r="K254" s="33"/>
       <c r="L254" s="2"/>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
@@ -7753,8 +7772,8 @@
       <c r="G255" s="1"/>
       <c r="H255" s="1"/>
       <c r="I255" s="1"/>
-      <c r="J255" s="1"/>
-      <c r="K255" s="1"/>
+      <c r="J255" s="33"/>
+      <c r="K255" s="33"/>
       <c r="L255" s="2"/>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
@@ -7781,8 +7800,8 @@
       <c r="G256" s="1"/>
       <c r="H256" s="1"/>
       <c r="I256" s="1"/>
-      <c r="J256" s="1"/>
-      <c r="K256" s="1"/>
+      <c r="J256" s="33"/>
+      <c r="K256" s="33"/>
       <c r="L256" s="2"/>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
@@ -7809,8 +7828,8 @@
       <c r="G257" s="1"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
-      <c r="J257" s="1"/>
-      <c r="K257" s="1"/>
+      <c r="J257" s="33"/>
+      <c r="K257" s="33"/>
       <c r="L257" s="2"/>
       <c r="M257" s="1"/>
       <c r="N257" s="1"/>
@@ -7837,8 +7856,8 @@
       <c r="G258" s="1"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
-      <c r="J258" s="1"/>
-      <c r="K258" s="1"/>
+      <c r="J258" s="33"/>
+      <c r="K258" s="33"/>
       <c r="L258" s="2"/>
       <c r="M258" s="1"/>
       <c r="N258" s="1"/>
@@ -7865,8 +7884,8 @@
       <c r="G259" s="1"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
-      <c r="J259" s="1"/>
-      <c r="K259" s="1"/>
+      <c r="J259" s="33"/>
+      <c r="K259" s="33"/>
       <c r="L259" s="2"/>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
@@ -7893,8 +7912,8 @@
       <c r="G260" s="1"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
-      <c r="J260" s="1"/>
-      <c r="K260" s="1"/>
+      <c r="J260" s="33"/>
+      <c r="K260" s="33"/>
       <c r="L260" s="2"/>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
@@ -7921,8 +7940,8 @@
       <c r="G261" s="1"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
-      <c r="J261" s="1"/>
-      <c r="K261" s="1"/>
+      <c r="J261" s="33"/>
+      <c r="K261" s="33"/>
       <c r="L261" s="2"/>
       <c r="M261" s="1"/>
       <c r="N261" s="1"/>
@@ -7949,8 +7968,8 @@
       <c r="G262" s="1"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
-      <c r="J262" s="1"/>
-      <c r="K262" s="1"/>
+      <c r="J262" s="33"/>
+      <c r="K262" s="33"/>
       <c r="L262" s="2"/>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
@@ -7977,8 +7996,8 @@
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
-      <c r="J263" s="1"/>
-      <c r="K263" s="1"/>
+      <c r="J263" s="33"/>
+      <c r="K263" s="33"/>
       <c r="L263" s="2"/>
       <c r="M263" s="1"/>
       <c r="N263" s="1"/>
@@ -8005,8 +8024,8 @@
       <c r="G264" s="1"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
-      <c r="J264" s="1"/>
-      <c r="K264" s="1"/>
+      <c r="J264" s="33"/>
+      <c r="K264" s="33"/>
       <c r="L264" s="2"/>
       <c r="M264" s="1"/>
       <c r="N264" s="1"/>
@@ -8033,8 +8052,8 @@
       <c r="G265" s="1"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
-      <c r="J265" s="1"/>
-      <c r="K265" s="1"/>
+      <c r="J265" s="33"/>
+      <c r="K265" s="33"/>
       <c r="L265" s="2"/>
       <c r="M265" s="1"/>
       <c r="N265" s="1"/>
@@ -8061,8 +8080,8 @@
       <c r="G266" s="1"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
-      <c r="J266" s="1"/>
-      <c r="K266" s="1"/>
+      <c r="J266" s="33"/>
+      <c r="K266" s="33"/>
       <c r="L266" s="2"/>
       <c r="M266" s="1"/>
       <c r="N266" s="1"/>
@@ -8089,8 +8108,8 @@
       <c r="G267" s="1"/>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
-      <c r="J267" s="1"/>
-      <c r="K267" s="1"/>
+      <c r="J267" s="33"/>
+      <c r="K267" s="33"/>
       <c r="L267" s="2"/>
       <c r="M267" s="1"/>
       <c r="N267" s="1"/>
@@ -8117,8 +8136,8 @@
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
-      <c r="J268" s="1"/>
-      <c r="K268" s="1"/>
+      <c r="J268" s="33"/>
+      <c r="K268" s="33"/>
       <c r="L268" s="2"/>
       <c r="M268" s="1"/>
       <c r="N268" s="1"/>
@@ -8145,8 +8164,8 @@
       <c r="G269" s="1"/>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
-      <c r="J269" s="1"/>
-      <c r="K269" s="1"/>
+      <c r="J269" s="33"/>
+      <c r="K269" s="33"/>
       <c r="L269" s="2"/>
       <c r="M269" s="1"/>
       <c r="N269" s="1"/>
@@ -8173,8 +8192,8 @@
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
-      <c r="J270" s="1"/>
-      <c r="K270" s="1"/>
+      <c r="J270" s="33"/>
+      <c r="K270" s="33"/>
       <c r="L270" s="2"/>
       <c r="M270" s="1"/>
       <c r="N270" s="1"/>
@@ -8201,8 +8220,8 @@
       <c r="G271" s="1"/>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
-      <c r="J271" s="1"/>
-      <c r="K271" s="1"/>
+      <c r="J271" s="33"/>
+      <c r="K271" s="33"/>
       <c r="L271" s="2"/>
       <c r="M271" s="1"/>
       <c r="N271" s="1"/>
@@ -8229,8 +8248,8 @@
       <c r="G272" s="1"/>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
-      <c r="J272" s="1"/>
-      <c r="K272" s="1"/>
+      <c r="J272" s="33"/>
+      <c r="K272" s="33"/>
       <c r="L272" s="2"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
@@ -8257,8 +8276,8 @@
       <c r="G273" s="1"/>
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
-      <c r="J273" s="1"/>
-      <c r="K273" s="1"/>
+      <c r="J273" s="33"/>
+      <c r="K273" s="33"/>
       <c r="L273" s="2"/>
       <c r="M273" s="1"/>
       <c r="N273" s="1"/>
@@ -8285,8 +8304,8 @@
       <c r="G274" s="1"/>
       <c r="H274" s="1"/>
       <c r="I274" s="1"/>
-      <c r="J274" s="1"/>
-      <c r="K274" s="1"/>
+      <c r="J274" s="33"/>
+      <c r="K274" s="33"/>
       <c r="L274" s="2"/>
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
@@ -8313,8 +8332,8 @@
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
       <c r="I275" s="1"/>
-      <c r="J275" s="1"/>
-      <c r="K275" s="1"/>
+      <c r="J275" s="33"/>
+      <c r="K275" s="33"/>
       <c r="L275" s="2"/>
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
@@ -8341,8 +8360,8 @@
       <c r="G276" s="1"/>
       <c r="H276" s="1"/>
       <c r="I276" s="1"/>
-      <c r="J276" s="1"/>
-      <c r="K276" s="1"/>
+      <c r="J276" s="33"/>
+      <c r="K276" s="33"/>
       <c r="L276" s="2"/>
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
@@ -8369,8 +8388,8 @@
       <c r="G277" s="1"/>
       <c r="H277" s="1"/>
       <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
+      <c r="J277" s="33"/>
+      <c r="K277" s="33"/>
       <c r="L277" s="2"/>
       <c r="M277" s="1"/>
       <c r="N277" s="1"/>
@@ -8397,8 +8416,8 @@
       <c r="G278" s="1"/>
       <c r="H278" s="1"/>
       <c r="I278" s="1"/>
-      <c r="J278" s="1"/>
-      <c r="K278" s="1"/>
+      <c r="J278" s="33"/>
+      <c r="K278" s="33"/>
       <c r="L278" s="2"/>
       <c r="M278" s="1"/>
       <c r="N278" s="1"/>
@@ -8425,8 +8444,8 @@
       <c r="G279" s="1"/>
       <c r="H279" s="1"/>
       <c r="I279" s="1"/>
-      <c r="J279" s="1"/>
-      <c r="K279" s="1"/>
+      <c r="J279" s="33"/>
+      <c r="K279" s="33"/>
       <c r="L279" s="2"/>
       <c r="M279" s="1"/>
       <c r="N279" s="1"/>
@@ -8453,8 +8472,8 @@
       <c r="G280" s="1"/>
       <c r="H280" s="1"/>
       <c r="I280" s="1"/>
-      <c r="J280" s="1"/>
-      <c r="K280" s="1"/>
+      <c r="J280" s="33"/>
+      <c r="K280" s="33"/>
       <c r="L280" s="2"/>
       <c r="M280" s="1"/>
       <c r="N280" s="1"/>
@@ -8481,8 +8500,8 @@
       <c r="G281" s="1"/>
       <c r="H281" s="1"/>
       <c r="I281" s="1"/>
-      <c r="J281" s="1"/>
-      <c r="K281" s="1"/>
+      <c r="J281" s="33"/>
+      <c r="K281" s="33"/>
       <c r="L281" s="2"/>
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
@@ -8509,8 +8528,8 @@
       <c r="G282" s="1"/>
       <c r="H282" s="1"/>
       <c r="I282" s="1"/>
-      <c r="J282" s="1"/>
-      <c r="K282" s="1"/>
+      <c r="J282" s="33"/>
+      <c r="K282" s="33"/>
       <c r="L282" s="2"/>
       <c r="M282" s="1"/>
       <c r="N282" s="1"/>
@@ -8537,8 +8556,8 @@
       <c r="G283" s="1"/>
       <c r="H283" s="1"/>
       <c r="I283" s="1"/>
-      <c r="J283" s="1"/>
-      <c r="K283" s="1"/>
+      <c r="J283" s="33"/>
+      <c r="K283" s="33"/>
       <c r="L283" s="2"/>
       <c r="M283" s="1"/>
       <c r="N283" s="1"/>
@@ -8565,8 +8584,8 @@
       <c r="G284" s="1"/>
       <c r="H284" s="1"/>
       <c r="I284" s="1"/>
-      <c r="J284" s="1"/>
-      <c r="K284" s="1"/>
+      <c r="J284" s="33"/>
+      <c r="K284" s="33"/>
       <c r="L284" s="2"/>
       <c r="M284" s="1"/>
       <c r="N284" s="1"/>
@@ -8593,8 +8612,8 @@
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
       <c r="I285" s="1"/>
-      <c r="J285" s="1"/>
-      <c r="K285" s="1"/>
+      <c r="J285" s="33"/>
+      <c r="K285" s="33"/>
       <c r="L285" s="2"/>
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
@@ -8621,8 +8640,8 @@
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
       <c r="I286" s="1"/>
-      <c r="J286" s="1"/>
-      <c r="K286" s="1"/>
+      <c r="J286" s="33"/>
+      <c r="K286" s="33"/>
       <c r="L286" s="2"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
@@ -8649,8 +8668,8 @@
       <c r="G287" s="1"/>
       <c r="H287" s="1"/>
       <c r="I287" s="1"/>
-      <c r="J287" s="1"/>
-      <c r="K287" s="1"/>
+      <c r="J287" s="33"/>
+      <c r="K287" s="33"/>
       <c r="L287" s="2"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
@@ -8677,8 +8696,8 @@
       <c r="G288" s="1"/>
       <c r="H288" s="1"/>
       <c r="I288" s="1"/>
-      <c r="J288" s="1"/>
-      <c r="K288" s="1"/>
+      <c r="J288" s="33"/>
+      <c r="K288" s="33"/>
       <c r="L288" s="2"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
@@ -8705,8 +8724,8 @@
       <c r="G289" s="1"/>
       <c r="H289" s="1"/>
       <c r="I289" s="1"/>
-      <c r="J289" s="1"/>
-      <c r="K289" s="1"/>
+      <c r="J289" s="33"/>
+      <c r="K289" s="33"/>
       <c r="L289" s="2"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
@@ -8733,8 +8752,8 @@
       <c r="G290" s="1"/>
       <c r="H290" s="1"/>
       <c r="I290" s="1"/>
-      <c r="J290" s="1"/>
-      <c r="K290" s="1"/>
+      <c r="J290" s="33"/>
+      <c r="K290" s="33"/>
       <c r="L290" s="2"/>
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
@@ -8761,8 +8780,8 @@
       <c r="G291" s="1"/>
       <c r="H291" s="1"/>
       <c r="I291" s="1"/>
-      <c r="J291" s="1"/>
-      <c r="K291" s="1"/>
+      <c r="J291" s="33"/>
+      <c r="K291" s="33"/>
       <c r="L291" s="2"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
@@ -8789,8 +8808,8 @@
       <c r="G292" s="1"/>
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
-      <c r="J292" s="1"/>
-      <c r="K292" s="1"/>
+      <c r="J292" s="33"/>
+      <c r="K292" s="33"/>
       <c r="L292" s="2"/>
       <c r="M292" s="1"/>
       <c r="N292" s="1"/>
@@ -8817,8 +8836,8 @@
       <c r="G293" s="1"/>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
-      <c r="J293" s="1"/>
-      <c r="K293" s="1"/>
+      <c r="J293" s="33"/>
+      <c r="K293" s="33"/>
       <c r="L293" s="2"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
@@ -8845,8 +8864,8 @@
       <c r="G294" s="1"/>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
-      <c r="J294" s="1"/>
-      <c r="K294" s="1"/>
+      <c r="J294" s="33"/>
+      <c r="K294" s="33"/>
       <c r="L294" s="2"/>
       <c r="M294" s="1"/>
       <c r="N294" s="1"/>
@@ -8873,8 +8892,8 @@
       <c r="G295" s="1"/>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
-      <c r="J295" s="1"/>
-      <c r="K295" s="1"/>
+      <c r="J295" s="33"/>
+      <c r="K295" s="33"/>
       <c r="L295" s="2"/>
       <c r="M295" s="1"/>
       <c r="N295" s="1"/>
@@ -8901,8 +8920,8 @@
       <c r="G296" s="1"/>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
-      <c r="J296" s="1"/>
-      <c r="K296" s="1"/>
+      <c r="J296" s="33"/>
+      <c r="K296" s="33"/>
       <c r="L296" s="2"/>
       <c r="M296" s="1"/>
       <c r="N296" s="1"/>
@@ -8929,8 +8948,8 @@
       <c r="G297" s="1"/>
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
-      <c r="J297" s="1"/>
-      <c r="K297" s="1"/>
+      <c r="J297" s="33"/>
+      <c r="K297" s="33"/>
       <c r="L297" s="2"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
@@ -8957,8 +8976,8 @@
       <c r="G298" s="1"/>
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
-      <c r="J298" s="1"/>
-      <c r="K298" s="1"/>
+      <c r="J298" s="33"/>
+      <c r="K298" s="33"/>
       <c r="L298" s="2"/>
       <c r="M298" s="1"/>
       <c r="N298" s="1"/>
@@ -8985,8 +9004,8 @@
       <c r="G299" s="1"/>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
-      <c r="J299" s="1"/>
-      <c r="K299" s="1"/>
+      <c r="J299" s="33"/>
+      <c r="K299" s="33"/>
       <c r="L299" s="2"/>
       <c r="M299" s="1"/>
       <c r="N299" s="1"/>
@@ -9013,8 +9032,8 @@
       <c r="G300" s="1"/>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
-      <c r="J300" s="1"/>
-      <c r="K300" s="1"/>
+      <c r="J300" s="33"/>
+      <c r="K300" s="33"/>
       <c r="L300" s="2"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
@@ -9041,8 +9060,8 @@
       <c r="G301" s="1"/>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
-      <c r="J301" s="1"/>
-      <c r="K301" s="1"/>
+      <c r="J301" s="33"/>
+      <c r="K301" s="33"/>
       <c r="L301" s="2"/>
       <c r="M301" s="1"/>
       <c r="N301" s="1"/>
@@ -9069,8 +9088,8 @@
       <c r="G302" s="1"/>
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
-      <c r="J302" s="1"/>
-      <c r="K302" s="1"/>
+      <c r="J302" s="33"/>
+      <c r="K302" s="33"/>
       <c r="L302" s="2"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
@@ -9097,8 +9116,8 @@
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
       <c r="I303" s="1"/>
-      <c r="J303" s="1"/>
-      <c r="K303" s="1"/>
+      <c r="J303" s="33"/>
+      <c r="K303" s="33"/>
       <c r="L303" s="2"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
@@ -9125,8 +9144,8 @@
       <c r="G304" s="1"/>
       <c r="H304" s="1"/>
       <c r="I304" s="1"/>
-      <c r="J304" s="1"/>
-      <c r="K304" s="1"/>
+      <c r="J304" s="33"/>
+      <c r="K304" s="33"/>
       <c r="L304" s="2"/>
       <c r="M304" s="1"/>
       <c r="N304" s="1"/>
@@ -9153,8 +9172,8 @@
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
       <c r="I305" s="1"/>
-      <c r="J305" s="1"/>
-      <c r="K305" s="1"/>
+      <c r="J305" s="33"/>
+      <c r="K305" s="33"/>
       <c r="L305" s="2"/>
       <c r="M305" s="1"/>
       <c r="N305" s="1"/>
@@ -9181,8 +9200,8 @@
       <c r="G306" s="1"/>
       <c r="H306" s="1"/>
       <c r="I306" s="1"/>
-      <c r="J306" s="1"/>
-      <c r="K306" s="1"/>
+      <c r="J306" s="33"/>
+      <c r="K306" s="33"/>
       <c r="L306" s="2"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
@@ -9209,8 +9228,8 @@
       <c r="G307" s="1"/>
       <c r="H307" s="1"/>
       <c r="I307" s="1"/>
-      <c r="J307" s="1"/>
-      <c r="K307" s="1"/>
+      <c r="J307" s="33"/>
+      <c r="K307" s="33"/>
       <c r="L307" s="2"/>
       <c r="M307" s="1"/>
       <c r="N307" s="1"/>
@@ -9237,8 +9256,8 @@
       <c r="G308" s="1"/>
       <c r="H308" s="1"/>
       <c r="I308" s="1"/>
-      <c r="J308" s="1"/>
-      <c r="K308" s="1"/>
+      <c r="J308" s="33"/>
+      <c r="K308" s="33"/>
       <c r="L308" s="2"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
@@ -9265,8 +9284,8 @@
       <c r="G309" s="1"/>
       <c r="H309" s="1"/>
       <c r="I309" s="1"/>
-      <c r="J309" s="1"/>
-      <c r="K309" s="1"/>
+      <c r="J309" s="33"/>
+      <c r="K309" s="33"/>
       <c r="L309" s="2"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
@@ -9293,8 +9312,8 @@
       <c r="G310" s="1"/>
       <c r="H310" s="1"/>
       <c r="I310" s="1"/>
-      <c r="J310" s="1"/>
-      <c r="K310" s="1"/>
+      <c r="J310" s="33"/>
+      <c r="K310" s="33"/>
       <c r="L310" s="2"/>
       <c r="M310" s="1"/>
       <c r="N310" s="1"/>
@@ -9321,8 +9340,8 @@
       <c r="G311" s="1"/>
       <c r="H311" s="1"/>
       <c r="I311" s="1"/>
-      <c r="J311" s="1"/>
-      <c r="K311" s="1"/>
+      <c r="J311" s="33"/>
+      <c r="K311" s="33"/>
       <c r="L311" s="2"/>
       <c r="M311" s="1"/>
       <c r="N311" s="1"/>
@@ -9349,8 +9368,8 @@
       <c r="G312" s="1"/>
       <c r="H312" s="1"/>
       <c r="I312" s="1"/>
-      <c r="J312" s="1"/>
-      <c r="K312" s="1"/>
+      <c r="J312" s="33"/>
+      <c r="K312" s="33"/>
       <c r="L312" s="2"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
@@ -9377,8 +9396,8 @@
       <c r="G313" s="1"/>
       <c r="H313" s="1"/>
       <c r="I313" s="1"/>
-      <c r="J313" s="1"/>
-      <c r="K313" s="1"/>
+      <c r="J313" s="33"/>
+      <c r="K313" s="33"/>
       <c r="L313" s="2"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
@@ -9405,8 +9424,8 @@
       <c r="G314" s="1"/>
       <c r="H314" s="1"/>
       <c r="I314" s="1"/>
-      <c r="J314" s="1"/>
-      <c r="K314" s="1"/>
+      <c r="J314" s="33"/>
+      <c r="K314" s="33"/>
       <c r="L314" s="2"/>
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
@@ -9433,8 +9452,8 @@
       <c r="G315" s="1"/>
       <c r="H315" s="1"/>
       <c r="I315" s="1"/>
-      <c r="J315" s="1"/>
-      <c r="K315" s="1"/>
+      <c r="J315" s="33"/>
+      <c r="K315" s="33"/>
       <c r="L315" s="2"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
@@ -9461,8 +9480,8 @@
       <c r="G316" s="1"/>
       <c r="H316" s="1"/>
       <c r="I316" s="1"/>
-      <c r="J316" s="1"/>
-      <c r="K316" s="1"/>
+      <c r="J316" s="33"/>
+      <c r="K316" s="33"/>
       <c r="L316" s="2"/>
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
@@ -9489,8 +9508,8 @@
       <c r="G317" s="1"/>
       <c r="H317" s="1"/>
       <c r="I317" s="1"/>
-      <c r="J317" s="1"/>
-      <c r="K317" s="1"/>
+      <c r="J317" s="33"/>
+      <c r="K317" s="33"/>
       <c r="L317" s="2"/>
       <c r="M317" s="1"/>
       <c r="N317" s="1"/>
@@ -9517,8 +9536,8 @@
       <c r="G318" s="1"/>
       <c r="H318" s="1"/>
       <c r="I318" s="1"/>
-      <c r="J318" s="1"/>
-      <c r="K318" s="1"/>
+      <c r="J318" s="33"/>
+      <c r="K318" s="33"/>
       <c r="L318" s="2"/>
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
@@ -9545,8 +9564,8 @@
       <c r="G319" s="1"/>
       <c r="H319" s="1"/>
       <c r="I319" s="1"/>
-      <c r="J319" s="1"/>
-      <c r="K319" s="1"/>
+      <c r="J319" s="33"/>
+      <c r="K319" s="33"/>
       <c r="L319" s="2"/>
       <c r="M319" s="1"/>
       <c r="N319" s="1"/>
@@ -9573,8 +9592,8 @@
       <c r="G320" s="1"/>
       <c r="H320" s="1"/>
       <c r="I320" s="1"/>
-      <c r="J320" s="1"/>
-      <c r="K320" s="1"/>
+      <c r="J320" s="33"/>
+      <c r="K320" s="33"/>
       <c r="L320" s="2"/>
       <c r="M320" s="1"/>
       <c r="N320" s="1"/>
@@ -9601,8 +9620,8 @@
       <c r="G321" s="1"/>
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
-      <c r="J321" s="1"/>
-      <c r="K321" s="1"/>
+      <c r="J321" s="33"/>
+      <c r="K321" s="33"/>
       <c r="L321" s="2"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
@@ -9629,8 +9648,8 @@
       <c r="G322" s="1"/>
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
-      <c r="J322" s="1"/>
-      <c r="K322" s="1"/>
+      <c r="J322" s="33"/>
+      <c r="K322" s="33"/>
       <c r="L322" s="2"/>
       <c r="M322" s="1"/>
       <c r="N322" s="1"/>
@@ -9657,8 +9676,8 @@
       <c r="G323" s="1"/>
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
-      <c r="J323" s="1"/>
-      <c r="K323" s="1"/>
+      <c r="J323" s="33"/>
+      <c r="K323" s="33"/>
       <c r="L323" s="2"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
@@ -9685,8 +9704,8 @@
       <c r="G324" s="1"/>
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
-      <c r="J324" s="1"/>
-      <c r="K324" s="1"/>
+      <c r="J324" s="33"/>
+      <c r="K324" s="33"/>
       <c r="L324" s="2"/>
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
@@ -9713,8 +9732,8 @@
       <c r="G325" s="1"/>
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
-      <c r="J325" s="1"/>
-      <c r="K325" s="1"/>
+      <c r="J325" s="33"/>
+      <c r="K325" s="33"/>
       <c r="L325" s="2"/>
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
@@ -9741,8 +9760,8 @@
       <c r="G326" s="1"/>
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
-      <c r="J326" s="1"/>
-      <c r="K326" s="1"/>
+      <c r="J326" s="33"/>
+      <c r="K326" s="33"/>
       <c r="L326" s="2"/>
       <c r="M326" s="1"/>
       <c r="N326" s="1"/>
@@ -9769,8 +9788,8 @@
       <c r="G327" s="1"/>
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
-      <c r="J327" s="1"/>
-      <c r="K327" s="1"/>
+      <c r="J327" s="33"/>
+      <c r="K327" s="33"/>
       <c r="L327" s="2"/>
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
@@ -9797,8 +9816,8 @@
       <c r="G328" s="1"/>
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
-      <c r="J328" s="1"/>
-      <c r="K328" s="1"/>
+      <c r="J328" s="33"/>
+      <c r="K328" s="33"/>
       <c r="L328" s="2"/>
       <c r="M328" s="1"/>
       <c r="N328" s="1"/>
@@ -9825,8 +9844,8 @@
       <c r="G329" s="1"/>
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
-      <c r="J329" s="1"/>
-      <c r="K329" s="1"/>
+      <c r="J329" s="33"/>
+      <c r="K329" s="33"/>
       <c r="L329" s="2"/>
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
@@ -9853,8 +9872,8 @@
       <c r="G330" s="1"/>
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
-      <c r="J330" s="1"/>
-      <c r="K330" s="1"/>
+      <c r="J330" s="33"/>
+      <c r="K330" s="33"/>
       <c r="L330" s="2"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
@@ -9881,8 +9900,8 @@
       <c r="G331" s="1"/>
       <c r="H331" s="1"/>
       <c r="I331" s="1"/>
-      <c r="J331" s="1"/>
-      <c r="K331" s="1"/>
+      <c r="J331" s="33"/>
+      <c r="K331" s="33"/>
       <c r="L331" s="2"/>
       <c r="M331" s="1"/>
       <c r="N331" s="1"/>
@@ -9909,8 +9928,8 @@
       <c r="G332" s="1"/>
       <c r="H332" s="1"/>
       <c r="I332" s="1"/>
-      <c r="J332" s="1"/>
-      <c r="K332" s="1"/>
+      <c r="J332" s="33"/>
+      <c r="K332" s="33"/>
       <c r="L332" s="2"/>
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
@@ -9937,8 +9956,8 @@
       <c r="G333" s="1"/>
       <c r="H333" s="1"/>
       <c r="I333" s="1"/>
-      <c r="J333" s="1"/>
-      <c r="K333" s="1"/>
+      <c r="J333" s="33"/>
+      <c r="K333" s="33"/>
       <c r="L333" s="2"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
@@ -9965,8 +9984,8 @@
       <c r="G334" s="1"/>
       <c r="H334" s="1"/>
       <c r="I334" s="1"/>
-      <c r="J334" s="1"/>
-      <c r="K334" s="1"/>
+      <c r="J334" s="33"/>
+      <c r="K334" s="33"/>
       <c r="L334" s="2"/>
       <c r="M334" s="1"/>
       <c r="N334" s="1"/>
@@ -9993,8 +10012,8 @@
       <c r="G335" s="1"/>
       <c r="H335" s="1"/>
       <c r="I335" s="1"/>
-      <c r="J335" s="1"/>
-      <c r="K335" s="1"/>
+      <c r="J335" s="33"/>
+      <c r="K335" s="33"/>
       <c r="L335" s="2"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
@@ -10021,8 +10040,8 @@
       <c r="G336" s="1"/>
       <c r="H336" s="1"/>
       <c r="I336" s="1"/>
-      <c r="J336" s="1"/>
-      <c r="K336" s="1"/>
+      <c r="J336" s="33"/>
+      <c r="K336" s="33"/>
       <c r="L336" s="2"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
@@ -10049,8 +10068,8 @@
       <c r="G337" s="1"/>
       <c r="H337" s="1"/>
       <c r="I337" s="1"/>
-      <c r="J337" s="1"/>
-      <c r="K337" s="1"/>
+      <c r="J337" s="33"/>
+      <c r="K337" s="33"/>
       <c r="L337" s="2"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
@@ -10077,8 +10096,8 @@
       <c r="G338" s="1"/>
       <c r="H338" s="1"/>
       <c r="I338" s="1"/>
-      <c r="J338" s="1"/>
-      <c r="K338" s="1"/>
+      <c r="J338" s="33"/>
+      <c r="K338" s="33"/>
       <c r="L338" s="2"/>
       <c r="M338" s="1"/>
       <c r="N338" s="1"/>
@@ -10105,8 +10124,8 @@
       <c r="G339" s="1"/>
       <c r="H339" s="1"/>
       <c r="I339" s="1"/>
-      <c r="J339" s="1"/>
-      <c r="K339" s="1"/>
+      <c r="J339" s="33"/>
+      <c r="K339" s="33"/>
       <c r="L339" s="2"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
@@ -10133,8 +10152,8 @@
       <c r="G340" s="1"/>
       <c r="H340" s="1"/>
       <c r="I340" s="1"/>
-      <c r="J340" s="1"/>
-      <c r="K340" s="1"/>
+      <c r="J340" s="33"/>
+      <c r="K340" s="33"/>
       <c r="L340" s="2"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
@@ -10161,8 +10180,8 @@
       <c r="G341" s="1"/>
       <c r="H341" s="1"/>
       <c r="I341" s="1"/>
-      <c r="J341" s="1"/>
-      <c r="K341" s="1"/>
+      <c r="J341" s="33"/>
+      <c r="K341" s="33"/>
       <c r="L341" s="2"/>
       <c r="M341" s="1"/>
       <c r="N341" s="1"/>
@@ -10189,8 +10208,8 @@
       <c r="G342" s="1"/>
       <c r="H342" s="1"/>
       <c r="I342" s="1"/>
-      <c r="J342" s="1"/>
-      <c r="K342" s="1"/>
+      <c r="J342" s="33"/>
+      <c r="K342" s="33"/>
       <c r="L342" s="2"/>
       <c r="M342" s="1"/>
       <c r="N342" s="1"/>
@@ -10217,8 +10236,8 @@
       <c r="G343" s="1"/>
       <c r="H343" s="1"/>
       <c r="I343" s="1"/>
-      <c r="J343" s="1"/>
-      <c r="K343" s="1"/>
+      <c r="J343" s="33"/>
+      <c r="K343" s="33"/>
       <c r="L343" s="2"/>
       <c r="M343" s="1"/>
       <c r="N343" s="1"/>
@@ -10245,8 +10264,8 @@
       <c r="G344" s="1"/>
       <c r="H344" s="1"/>
       <c r="I344" s="1"/>
-      <c r="J344" s="1"/>
-      <c r="K344" s="1"/>
+      <c r="J344" s="33"/>
+      <c r="K344" s="33"/>
       <c r="L344" s="2"/>
       <c r="M344" s="1"/>
       <c r="N344" s="1"/>
@@ -10273,8 +10292,8 @@
       <c r="G345" s="1"/>
       <c r="H345" s="1"/>
       <c r="I345" s="1"/>
-      <c r="J345" s="1"/>
-      <c r="K345" s="1"/>
+      <c r="J345" s="33"/>
+      <c r="K345" s="33"/>
       <c r="L345" s="2"/>
       <c r="M345" s="1"/>
       <c r="N345" s="1"/>
@@ -10301,8 +10320,8 @@
       <c r="G346" s="1"/>
       <c r="H346" s="1"/>
       <c r="I346" s="1"/>
-      <c r="J346" s="1"/>
-      <c r="K346" s="1"/>
+      <c r="J346" s="33"/>
+      <c r="K346" s="33"/>
       <c r="L346" s="2"/>
       <c r="M346" s="1"/>
       <c r="N346" s="1"/>
@@ -10329,8 +10348,8 @@
       <c r="G347" s="1"/>
       <c r="H347" s="1"/>
       <c r="I347" s="1"/>
-      <c r="J347" s="1"/>
-      <c r="K347" s="1"/>
+      <c r="J347" s="33"/>
+      <c r="K347" s="33"/>
       <c r="L347" s="2"/>
       <c r="M347" s="1"/>
       <c r="N347" s="1"/>
@@ -10357,8 +10376,8 @@
       <c r="G348" s="1"/>
       <c r="H348" s="1"/>
       <c r="I348" s="1"/>
-      <c r="J348" s="1"/>
-      <c r="K348" s="1"/>
+      <c r="J348" s="33"/>
+      <c r="K348" s="33"/>
       <c r="L348" s="2"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
@@ -10385,8 +10404,8 @@
       <c r="G349" s="1"/>
       <c r="H349" s="1"/>
       <c r="I349" s="1"/>
-      <c r="J349" s="1"/>
-      <c r="K349" s="1"/>
+      <c r="J349" s="33"/>
+      <c r="K349" s="33"/>
       <c r="L349" s="2"/>
       <c r="M349" s="1"/>
       <c r="N349" s="1"/>
@@ -10413,8 +10432,8 @@
       <c r="G350" s="1"/>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
-      <c r="J350" s="1"/>
-      <c r="K350" s="1"/>
+      <c r="J350" s="33"/>
+      <c r="K350" s="33"/>
       <c r="L350" s="2"/>
       <c r="M350" s="1"/>
       <c r="N350" s="1"/>
@@ -10441,8 +10460,8 @@
       <c r="G351" s="1"/>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
-      <c r="J351" s="1"/>
-      <c r="K351" s="1"/>
+      <c r="J351" s="33"/>
+      <c r="K351" s="33"/>
       <c r="L351" s="2"/>
       <c r="M351" s="1"/>
       <c r="N351" s="1"/>
@@ -10469,8 +10488,8 @@
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
-      <c r="J352" s="1"/>
-      <c r="K352" s="1"/>
+      <c r="J352" s="33"/>
+      <c r="K352" s="33"/>
       <c r="L352" s="2"/>
       <c r="M352" s="1"/>
       <c r="N352" s="1"/>
@@ -10497,8 +10516,8 @@
       <c r="G353" s="1"/>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
-      <c r="J353" s="1"/>
-      <c r="K353" s="1"/>
+      <c r="J353" s="33"/>
+      <c r="K353" s="33"/>
       <c r="L353" s="2"/>
       <c r="M353" s="1"/>
       <c r="N353" s="1"/>
@@ -10525,8 +10544,8 @@
       <c r="G354" s="1"/>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
-      <c r="J354" s="1"/>
-      <c r="K354" s="1"/>
+      <c r="J354" s="33"/>
+      <c r="K354" s="33"/>
       <c r="L354" s="2"/>
       <c r="M354" s="1"/>
       <c r="N354" s="1"/>
@@ -10553,8 +10572,8 @@
       <c r="G355" s="1"/>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
-      <c r="J355" s="1"/>
-      <c r="K355" s="1"/>
+      <c r="J355" s="33"/>
+      <c r="K355" s="33"/>
       <c r="L355" s="2"/>
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
@@ -10581,8 +10600,8 @@
       <c r="G356" s="1"/>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
-      <c r="J356" s="1"/>
-      <c r="K356" s="1"/>
+      <c r="J356" s="33"/>
+      <c r="K356" s="33"/>
       <c r="L356" s="2"/>
       <c r="M356" s="1"/>
       <c r="N356" s="1"/>
@@ -10609,8 +10628,8 @@
       <c r="G357" s="1"/>
       <c r="H357" s="1"/>
       <c r="I357" s="1"/>
-      <c r="J357" s="1"/>
-      <c r="K357" s="1"/>
+      <c r="J357" s="33"/>
+      <c r="K357" s="33"/>
       <c r="L357" s="2"/>
       <c r="M357" s="1"/>
       <c r="N357" s="1"/>
@@ -10637,8 +10656,8 @@
       <c r="G358" s="1"/>
       <c r="H358" s="1"/>
       <c r="I358" s="1"/>
-      <c r="J358" s="1"/>
-      <c r="K358" s="1"/>
+      <c r="J358" s="33"/>
+      <c r="K358" s="33"/>
       <c r="L358" s="2"/>
       <c r="M358" s="1"/>
       <c r="N358" s="1"/>
@@ -10665,8 +10684,8 @@
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
       <c r="I359" s="1"/>
-      <c r="J359" s="1"/>
-      <c r="K359" s="1"/>
+      <c r="J359" s="33"/>
+      <c r="K359" s="33"/>
       <c r="L359" s="2"/>
       <c r="M359" s="1"/>
       <c r="N359" s="1"/>
@@ -10693,8 +10712,8 @@
       <c r="G360" s="1"/>
       <c r="H360" s="1"/>
       <c r="I360" s="1"/>
-      <c r="J360" s="1"/>
-      <c r="K360" s="1"/>
+      <c r="J360" s="33"/>
+      <c r="K360" s="33"/>
       <c r="L360" s="2"/>
       <c r="M360" s="1"/>
       <c r="N360" s="1"/>
@@ -10721,8 +10740,8 @@
       <c r="G361" s="1"/>
       <c r="H361" s="1"/>
       <c r="I361" s="1"/>
-      <c r="J361" s="1"/>
-      <c r="K361" s="1"/>
+      <c r="J361" s="33"/>
+      <c r="K361" s="33"/>
       <c r="L361" s="2"/>
       <c r="M361" s="1"/>
       <c r="N361" s="1"/>
@@ -10749,8 +10768,8 @@
       <c r="G362" s="1"/>
       <c r="H362" s="1"/>
       <c r="I362" s="1"/>
-      <c r="J362" s="1"/>
-      <c r="K362" s="1"/>
+      <c r="J362" s="33"/>
+      <c r="K362" s="33"/>
       <c r="L362" s="2"/>
       <c r="M362" s="1"/>
       <c r="N362" s="1"/>
@@ -10777,8 +10796,8 @@
       <c r="G363" s="1"/>
       <c r="H363" s="1"/>
       <c r="I363" s="1"/>
-      <c r="J363" s="1"/>
-      <c r="K363" s="1"/>
+      <c r="J363" s="33"/>
+      <c r="K363" s="33"/>
       <c r="L363" s="2"/>
       <c r="M363" s="1"/>
       <c r="N363" s="1"/>
@@ -10805,8 +10824,8 @@
       <c r="G364" s="1"/>
       <c r="H364" s="1"/>
       <c r="I364" s="1"/>
-      <c r="J364" s="1"/>
-      <c r="K364" s="1"/>
+      <c r="J364" s="33"/>
+      <c r="K364" s="33"/>
       <c r="L364" s="2"/>
       <c r="M364" s="1"/>
       <c r="N364" s="1"/>
@@ -10833,8 +10852,8 @@
       <c r="G365" s="1"/>
       <c r="H365" s="1"/>
       <c r="I365" s="1"/>
-      <c r="J365" s="1"/>
-      <c r="K365" s="1"/>
+      <c r="J365" s="33"/>
+      <c r="K365" s="33"/>
       <c r="L365" s="2"/>
       <c r="M365" s="1"/>
       <c r="N365" s="1"/>
@@ -10861,8 +10880,8 @@
       <c r="G366" s="1"/>
       <c r="H366" s="1"/>
       <c r="I366" s="1"/>
-      <c r="J366" s="1"/>
-      <c r="K366" s="1"/>
+      <c r="J366" s="33"/>
+      <c r="K366" s="33"/>
       <c r="L366" s="2"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
@@ -10889,8 +10908,8 @@
       <c r="G367" s="1"/>
       <c r="H367" s="1"/>
       <c r="I367" s="1"/>
-      <c r="J367" s="1"/>
-      <c r="K367" s="1"/>
+      <c r="J367" s="33"/>
+      <c r="K367" s="33"/>
       <c r="L367" s="2"/>
       <c r="M367" s="1"/>
       <c r="N367" s="1"/>
@@ -10917,8 +10936,8 @@
       <c r="G368" s="1"/>
       <c r="H368" s="1"/>
       <c r="I368" s="1"/>
-      <c r="J368" s="1"/>
-      <c r="K368" s="1"/>
+      <c r="J368" s="33"/>
+      <c r="K368" s="33"/>
       <c r="L368" s="2"/>
       <c r="M368" s="1"/>
       <c r="N368" s="1"/>
@@ -10945,8 +10964,8 @@
       <c r="G369" s="1"/>
       <c r="H369" s="1"/>
       <c r="I369" s="1"/>
-      <c r="J369" s="1"/>
-      <c r="K369" s="1"/>
+      <c r="J369" s="33"/>
+      <c r="K369" s="33"/>
       <c r="L369" s="2"/>
       <c r="M369" s="1"/>
       <c r="N369" s="1"/>
@@ -10973,8 +10992,8 @@
       <c r="G370" s="1"/>
       <c r="H370" s="1"/>
       <c r="I370" s="1"/>
-      <c r="J370" s="1"/>
-      <c r="K370" s="1"/>
+      <c r="J370" s="33"/>
+      <c r="K370" s="33"/>
       <c r="L370" s="2"/>
       <c r="M370" s="1"/>
       <c r="N370" s="1"/>
@@ -11001,8 +11020,8 @@
       <c r="G371" s="1"/>
       <c r="H371" s="1"/>
       <c r="I371" s="1"/>
-      <c r="J371" s="1"/>
-      <c r="K371" s="1"/>
+      <c r="J371" s="33"/>
+      <c r="K371" s="33"/>
       <c r="L371" s="2"/>
       <c r="M371" s="1"/>
       <c r="N371" s="1"/>
@@ -11029,8 +11048,8 @@
       <c r="G372" s="1"/>
       <c r="H372" s="1"/>
       <c r="I372" s="1"/>
-      <c r="J372" s="1"/>
-      <c r="K372" s="1"/>
+      <c r="J372" s="33"/>
+      <c r="K372" s="33"/>
       <c r="L372" s="2"/>
       <c r="M372" s="1"/>
       <c r="N372" s="1"/>
@@ -11057,8 +11076,8 @@
       <c r="G373" s="1"/>
       <c r="H373" s="1"/>
       <c r="I373" s="1"/>
-      <c r="J373" s="1"/>
-      <c r="K373" s="1"/>
+      <c r="J373" s="33"/>
+      <c r="K373" s="33"/>
       <c r="L373" s="2"/>
       <c r="M373" s="1"/>
       <c r="N373" s="1"/>
@@ -11085,8 +11104,8 @@
       <c r="G374" s="1"/>
       <c r="H374" s="1"/>
       <c r="I374" s="1"/>
-      <c r="J374" s="1"/>
-      <c r="K374" s="1"/>
+      <c r="J374" s="33"/>
+      <c r="K374" s="33"/>
       <c r="L374" s="2"/>
       <c r="M374" s="1"/>
       <c r="N374" s="1"/>
@@ -11113,8 +11132,8 @@
       <c r="G375" s="1"/>
       <c r="H375" s="1"/>
       <c r="I375" s="1"/>
-      <c r="J375" s="1"/>
-      <c r="K375" s="1"/>
+      <c r="J375" s="33"/>
+      <c r="K375" s="33"/>
       <c r="L375" s="2"/>
       <c r="M375" s="1"/>
       <c r="N375" s="1"/>
@@ -11141,8 +11160,8 @@
       <c r="G376" s="1"/>
       <c r="H376" s="1"/>
       <c r="I376" s="1"/>
-      <c r="J376" s="1"/>
-      <c r="K376" s="1"/>
+      <c r="J376" s="33"/>
+      <c r="K376" s="33"/>
       <c r="L376" s="2"/>
       <c r="M376" s="1"/>
       <c r="N376" s="1"/>
@@ -11169,8 +11188,8 @@
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
       <c r="I377" s="1"/>
-      <c r="J377" s="1"/>
-      <c r="K377" s="1"/>
+      <c r="J377" s="33"/>
+      <c r="K377" s="33"/>
       <c r="L377" s="2"/>
       <c r="M377" s="1"/>
       <c r="N377" s="1"/>
@@ -11197,8 +11216,8 @@
       <c r="G378" s="1"/>
       <c r="H378" s="1"/>
       <c r="I378" s="1"/>
-      <c r="J378" s="1"/>
-      <c r="K378" s="1"/>
+      <c r="J378" s="33"/>
+      <c r="K378" s="33"/>
       <c r="L378" s="2"/>
       <c r="M378" s="1"/>
       <c r="N378" s="1"/>
@@ -11225,8 +11244,8 @@
       <c r="G379" s="1"/>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
-      <c r="J379" s="1"/>
-      <c r="K379" s="1"/>
+      <c r="J379" s="33"/>
+      <c r="K379" s="33"/>
       <c r="L379" s="2"/>
       <c r="M379" s="1"/>
       <c r="N379" s="1"/>
@@ -11253,8 +11272,8 @@
       <c r="G380" s="1"/>
       <c r="H380" s="1"/>
       <c r="I380" s="1"/>
-      <c r="J380" s="1"/>
-      <c r="K380" s="1"/>
+      <c r="J380" s="33"/>
+      <c r="K380" s="33"/>
       <c r="L380" s="2"/>
       <c r="M380" s="1"/>
       <c r="N380" s="1"/>
@@ -11281,8 +11300,8 @@
       <c r="G381" s="1"/>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
-      <c r="J381" s="1"/>
-      <c r="K381" s="1"/>
+      <c r="J381" s="33"/>
+      <c r="K381" s="33"/>
       <c r="L381" s="2"/>
       <c r="M381" s="1"/>
       <c r="N381" s="1"/>
@@ -11309,8 +11328,8 @@
       <c r="G382" s="1"/>
       <c r="H382" s="1"/>
       <c r="I382" s="1"/>
-      <c r="J382" s="1"/>
-      <c r="K382" s="1"/>
+      <c r="J382" s="33"/>
+      <c r="K382" s="33"/>
       <c r="L382" s="2"/>
       <c r="M382" s="1"/>
       <c r="N382" s="1"/>
@@ -11337,8 +11356,8 @@
       <c r="G383" s="1"/>
       <c r="H383" s="1"/>
       <c r="I383" s="1"/>
-      <c r="J383" s="1"/>
-      <c r="K383" s="1"/>
+      <c r="J383" s="33"/>
+      <c r="K383" s="33"/>
       <c r="L383" s="2"/>
       <c r="M383" s="1"/>
       <c r="N383" s="1"/>
@@ -11365,8 +11384,8 @@
       <c r="G384" s="1"/>
       <c r="H384" s="1"/>
       <c r="I384" s="1"/>
-      <c r="J384" s="1"/>
-      <c r="K384" s="1"/>
+      <c r="J384" s="33"/>
+      <c r="K384" s="33"/>
       <c r="L384" s="2"/>
       <c r="M384" s="1"/>
       <c r="N384" s="1"/>
@@ -11393,8 +11412,8 @@
       <c r="G385" s="1"/>
       <c r="H385" s="1"/>
       <c r="I385" s="1"/>
-      <c r="J385" s="1"/>
-      <c r="K385" s="1"/>
+      <c r="J385" s="33"/>
+      <c r="K385" s="33"/>
       <c r="L385" s="2"/>
       <c r="M385" s="1"/>
       <c r="N385" s="1"/>
@@ -11421,8 +11440,8 @@
       <c r="G386" s="1"/>
       <c r="H386" s="1"/>
       <c r="I386" s="1"/>
-      <c r="J386" s="1"/>
-      <c r="K386" s="1"/>
+      <c r="J386" s="33"/>
+      <c r="K386" s="33"/>
       <c r="L386" s="2"/>
       <c r="M386" s="1"/>
       <c r="N386" s="1"/>
@@ -11449,8 +11468,8 @@
       <c r="G387" s="1"/>
       <c r="H387" s="1"/>
       <c r="I387" s="1"/>
-      <c r="J387" s="1"/>
-      <c r="K387" s="1"/>
+      <c r="J387" s="33"/>
+      <c r="K387" s="33"/>
       <c r="L387" s="2"/>
       <c r="M387" s="1"/>
       <c r="N387" s="1"/>
@@ -11477,8 +11496,8 @@
       <c r="G388" s="1"/>
       <c r="H388" s="1"/>
       <c r="I388" s="1"/>
-      <c r="J388" s="1"/>
-      <c r="K388" s="1"/>
+      <c r="J388" s="33"/>
+      <c r="K388" s="33"/>
       <c r="L388" s="2"/>
       <c r="M388" s="1"/>
       <c r="N388" s="1"/>
@@ -11505,8 +11524,8 @@
       <c r="G389" s="1"/>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
-      <c r="J389" s="1"/>
-      <c r="K389" s="1"/>
+      <c r="J389" s="33"/>
+      <c r="K389" s="33"/>
       <c r="L389" s="2"/>
       <c r="M389" s="1"/>
       <c r="N389" s="1"/>
@@ -11533,8 +11552,8 @@
       <c r="G390" s="1"/>
       <c r="H390" s="1"/>
       <c r="I390" s="1"/>
-      <c r="J390" s="1"/>
-      <c r="K390" s="1"/>
+      <c r="J390" s="33"/>
+      <c r="K390" s="33"/>
       <c r="L390" s="2"/>
       <c r="M390" s="1"/>
       <c r="N390" s="1"/>
@@ -11561,8 +11580,8 @@
       <c r="G391" s="1"/>
       <c r="H391" s="1"/>
       <c r="I391" s="1"/>
-      <c r="J391" s="1"/>
-      <c r="K391" s="1"/>
+      <c r="J391" s="33"/>
+      <c r="K391" s="33"/>
       <c r="L391" s="2"/>
       <c r="M391" s="1"/>
       <c r="N391" s="1"/>
@@ -11589,8 +11608,8 @@
       <c r="G392" s="1"/>
       <c r="H392" s="1"/>
       <c r="I392" s="1"/>
-      <c r="J392" s="1"/>
-      <c r="K392" s="1"/>
+      <c r="J392" s="33"/>
+      <c r="K392" s="33"/>
       <c r="L392" s="2"/>
       <c r="M392" s="1"/>
       <c r="N392" s="1"/>
@@ -11617,8 +11636,8 @@
       <c r="G393" s="1"/>
       <c r="H393" s="1"/>
       <c r="I393" s="1"/>
-      <c r="J393" s="1"/>
-      <c r="K393" s="1"/>
+      <c r="J393" s="33"/>
+      <c r="K393" s="33"/>
       <c r="L393" s="2"/>
       <c r="M393" s="1"/>
       <c r="N393" s="1"/>
@@ -11645,8 +11664,8 @@
       <c r="G394" s="1"/>
       <c r="H394" s="1"/>
       <c r="I394" s="1"/>
-      <c r="J394" s="1"/>
-      <c r="K394" s="1"/>
+      <c r="J394" s="33"/>
+      <c r="K394" s="33"/>
       <c r="L394" s="2"/>
       <c r="M394" s="1"/>
       <c r="N394" s="1"/>
@@ -11673,8 +11692,8 @@
       <c r="G395" s="1"/>
       <c r="H395" s="1"/>
       <c r="I395" s="1"/>
-      <c r="J395" s="1"/>
-      <c r="K395" s="1"/>
+      <c r="J395" s="33"/>
+      <c r="K395" s="33"/>
       <c r="L395" s="2"/>
       <c r="M395" s="1"/>
       <c r="N395" s="1"/>
@@ -11701,8 +11720,8 @@
       <c r="G396" s="1"/>
       <c r="H396" s="1"/>
       <c r="I396" s="1"/>
-      <c r="J396" s="1"/>
-      <c r="K396" s="1"/>
+      <c r="J396" s="33"/>
+      <c r="K396" s="33"/>
       <c r="L396" s="2"/>
       <c r="M396" s="1"/>
       <c r="N396" s="1"/>
@@ -11729,8 +11748,8 @@
       <c r="G397" s="1"/>
       <c r="H397" s="1"/>
       <c r="I397" s="1"/>
-      <c r="J397" s="1"/>
-      <c r="K397" s="1"/>
+      <c r="J397" s="33"/>
+      <c r="K397" s="33"/>
       <c r="L397" s="2"/>
       <c r="M397" s="1"/>
       <c r="N397" s="1"/>
@@ -11757,8 +11776,8 @@
       <c r="G398" s="1"/>
       <c r="H398" s="1"/>
       <c r="I398" s="1"/>
-      <c r="J398" s="1"/>
-      <c r="K398" s="1"/>
+      <c r="J398" s="33"/>
+      <c r="K398" s="33"/>
       <c r="L398" s="2"/>
       <c r="M398" s="1"/>
       <c r="N398" s="1"/>
@@ -11785,8 +11804,8 @@
       <c r="G399" s="1"/>
       <c r="H399" s="1"/>
       <c r="I399" s="1"/>
-      <c r="J399" s="1"/>
-      <c r="K399" s="1"/>
+      <c r="J399" s="33"/>
+      <c r="K399" s="33"/>
       <c r="L399" s="2"/>
       <c r="M399" s="1"/>
       <c r="N399" s="1"/>
@@ -11813,8 +11832,8 @@
       <c r="G400" s="1"/>
       <c r="H400" s="1"/>
       <c r="I400" s="1"/>
-      <c r="J400" s="1"/>
-      <c r="K400" s="1"/>
+      <c r="J400" s="33"/>
+      <c r="K400" s="33"/>
       <c r="L400" s="2"/>
       <c r="M400" s="1"/>
       <c r="N400" s="1"/>
@@ -11841,8 +11860,8 @@
       <c r="G401" s="1"/>
       <c r="H401" s="1"/>
       <c r="I401" s="1"/>
-      <c r="J401" s="1"/>
-      <c r="K401" s="1"/>
+      <c r="J401" s="33"/>
+      <c r="K401" s="33"/>
       <c r="L401" s="2"/>
       <c r="M401" s="1"/>
       <c r="N401" s="1"/>
@@ -11869,8 +11888,8 @@
       <c r="G402" s="1"/>
       <c r="H402" s="1"/>
       <c r="I402" s="1"/>
-      <c r="J402" s="1"/>
-      <c r="K402" s="1"/>
+      <c r="J402" s="33"/>
+      <c r="K402" s="33"/>
       <c r="L402" s="2"/>
       <c r="M402" s="1"/>
       <c r="N402" s="1"/>
@@ -11897,8 +11916,8 @@
       <c r="G403" s="1"/>
       <c r="H403" s="1"/>
       <c r="I403" s="1"/>
-      <c r="J403" s="1"/>
-      <c r="K403" s="1"/>
+      <c r="J403" s="33"/>
+      <c r="K403" s="33"/>
       <c r="L403" s="2"/>
       <c r="M403" s="1"/>
       <c r="N403" s="1"/>
@@ -11925,8 +11944,8 @@
       <c r="G404" s="1"/>
       <c r="H404" s="1"/>
       <c r="I404" s="1"/>
-      <c r="J404" s="1"/>
-      <c r="K404" s="1"/>
+      <c r="J404" s="33"/>
+      <c r="K404" s="33"/>
       <c r="L404" s="2"/>
       <c r="M404" s="1"/>
       <c r="N404" s="1"/>
@@ -11953,8 +11972,8 @@
       <c r="G405" s="1"/>
       <c r="H405" s="1"/>
       <c r="I405" s="1"/>
-      <c r="J405" s="1"/>
-      <c r="K405" s="1"/>
+      <c r="J405" s="33"/>
+      <c r="K405" s="33"/>
       <c r="L405" s="2"/>
       <c r="M405" s="1"/>
       <c r="N405" s="1"/>
@@ -11981,8 +12000,8 @@
       <c r="G406" s="1"/>
       <c r="H406" s="1"/>
       <c r="I406" s="1"/>
-      <c r="J406" s="1"/>
-      <c r="K406" s="1"/>
+      <c r="J406" s="33"/>
+      <c r="K406" s="33"/>
       <c r="L406" s="2"/>
       <c r="M406" s="1"/>
       <c r="N406" s="1"/>
@@ -12009,8 +12028,8 @@
       <c r="G407" s="1"/>
       <c r="H407" s="1"/>
       <c r="I407" s="1"/>
-      <c r="J407" s="1"/>
-      <c r="K407" s="1"/>
+      <c r="J407" s="33"/>
+      <c r="K407" s="33"/>
       <c r="L407" s="2"/>
       <c r="M407" s="1"/>
       <c r="N407" s="1"/>
@@ -12037,8 +12056,8 @@
       <c r="G408" s="1"/>
       <c r="H408" s="1"/>
       <c r="I408" s="1"/>
-      <c r="J408" s="1"/>
-      <c r="K408" s="1"/>
+      <c r="J408" s="33"/>
+      <c r="K408" s="33"/>
       <c r="L408" s="2"/>
       <c r="M408" s="1"/>
       <c r="N408" s="1"/>
@@ -12065,8 +12084,8 @@
       <c r="G409" s="1"/>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
-      <c r="J409" s="1"/>
-      <c r="K409" s="1"/>
+      <c r="J409" s="33"/>
+      <c r="K409" s="33"/>
       <c r="L409" s="2"/>
       <c r="M409" s="1"/>
       <c r="N409" s="1"/>
@@ -12093,8 +12112,8 @@
       <c r="G410" s="1"/>
       <c r="H410" s="1"/>
       <c r="I410" s="1"/>
-      <c r="J410" s="1"/>
-      <c r="K410" s="1"/>
+      <c r="J410" s="33"/>
+      <c r="K410" s="33"/>
       <c r="L410" s="2"/>
       <c r="M410" s="1"/>
       <c r="N410" s="1"/>
@@ -12121,8 +12140,8 @@
       <c r="G411" s="1"/>
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
-      <c r="J411" s="1"/>
-      <c r="K411" s="1"/>
+      <c r="J411" s="33"/>
+      <c r="K411" s="33"/>
       <c r="L411" s="2"/>
       <c r="M411" s="1"/>
       <c r="N411" s="1"/>
@@ -12149,8 +12168,8 @@
       <c r="G412" s="1"/>
       <c r="H412" s="1"/>
       <c r="I412" s="1"/>
-      <c r="J412" s="1"/>
-      <c r="K412" s="1"/>
+      <c r="J412" s="33"/>
+      <c r="K412" s="33"/>
       <c r="L412" s="2"/>
       <c r="M412" s="1"/>
       <c r="N412" s="1"/>
@@ -12177,8 +12196,8 @@
       <c r="G413" s="1"/>
       <c r="H413" s="1"/>
       <c r="I413" s="1"/>
-      <c r="J413" s="1"/>
-      <c r="K413" s="1"/>
+      <c r="J413" s="33"/>
+      <c r="K413" s="33"/>
       <c r="L413" s="2"/>
       <c r="M413" s="1"/>
       <c r="N413" s="1"/>
@@ -12205,8 +12224,8 @@
       <c r="G414" s="1"/>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
-      <c r="J414" s="1"/>
-      <c r="K414" s="1"/>
+      <c r="J414" s="33"/>
+      <c r="K414" s="33"/>
       <c r="L414" s="2"/>
       <c r="M414" s="1"/>
       <c r="N414" s="1"/>
@@ -12233,8 +12252,8 @@
       <c r="G415" s="1"/>
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
-      <c r="J415" s="1"/>
-      <c r="K415" s="1"/>
+      <c r="J415" s="33"/>
+      <c r="K415" s="33"/>
       <c r="L415" s="2"/>
       <c r="M415" s="1"/>
       <c r="N415" s="1"/>
@@ -12261,8 +12280,8 @@
       <c r="G416" s="1"/>
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
-      <c r="J416" s="1"/>
-      <c r="K416" s="1"/>
+      <c r="J416" s="33"/>
+      <c r="K416" s="33"/>
       <c r="L416" s="2"/>
       <c r="M416" s="1"/>
       <c r="N416" s="1"/>
@@ -12289,8 +12308,8 @@
       <c r="G417" s="1"/>
       <c r="H417" s="1"/>
       <c r="I417" s="1"/>
-      <c r="J417" s="1"/>
-      <c r="K417" s="1"/>
+      <c r="J417" s="33"/>
+      <c r="K417" s="33"/>
       <c r="L417" s="2"/>
       <c r="M417" s="1"/>
       <c r="N417" s="1"/>
@@ -12317,8 +12336,8 @@
       <c r="G418" s="1"/>
       <c r="H418" s="1"/>
       <c r="I418" s="1"/>
-      <c r="J418" s="1"/>
-      <c r="K418" s="1"/>
+      <c r="J418" s="33"/>
+      <c r="K418" s="33"/>
       <c r="L418" s="2"/>
       <c r="M418" s="1"/>
       <c r="N418" s="1"/>
@@ -12345,8 +12364,8 @@
       <c r="G419" s="1"/>
       <c r="H419" s="1"/>
       <c r="I419" s="1"/>
-      <c r="J419" s="1"/>
-      <c r="K419" s="1"/>
+      <c r="J419" s="33"/>
+      <c r="K419" s="33"/>
       <c r="L419" s="2"/>
       <c r="M419" s="1"/>
       <c r="N419" s="1"/>
@@ -12373,8 +12392,8 @@
       <c r="G420" s="1"/>
       <c r="H420" s="1"/>
       <c r="I420" s="1"/>
-      <c r="J420" s="1"/>
-      <c r="K420" s="1"/>
+      <c r="J420" s="33"/>
+      <c r="K420" s="33"/>
       <c r="L420" s="2"/>
       <c r="M420" s="1"/>
       <c r="N420" s="1"/>
@@ -12401,8 +12420,8 @@
       <c r="G421" s="1"/>
       <c r="H421" s="1"/>
       <c r="I421" s="1"/>
-      <c r="J421" s="1"/>
-      <c r="K421" s="1"/>
+      <c r="J421" s="33"/>
+      <c r="K421" s="33"/>
       <c r="L421" s="2"/>
       <c r="M421" s="1"/>
       <c r="N421" s="1"/>
@@ -12429,8 +12448,8 @@
       <c r="G422" s="1"/>
       <c r="H422" s="1"/>
       <c r="I422" s="1"/>
-      <c r="J422" s="1"/>
-      <c r="K422" s="1"/>
+      <c r="J422" s="33"/>
+      <c r="K422" s="33"/>
       <c r="L422" s="2"/>
       <c r="M422" s="1"/>
       <c r="N422" s="1"/>
@@ -12457,8 +12476,8 @@
       <c r="G423" s="1"/>
       <c r="H423" s="1"/>
       <c r="I423" s="1"/>
-      <c r="J423" s="1"/>
-      <c r="K423" s="1"/>
+      <c r="J423" s="33"/>
+      <c r="K423" s="33"/>
       <c r="L423" s="2"/>
       <c r="M423" s="1"/>
       <c r="N423" s="1"/>
@@ -12485,8 +12504,8 @@
       <c r="G424" s="1"/>
       <c r="H424" s="1"/>
       <c r="I424" s="1"/>
-      <c r="J424" s="1"/>
-      <c r="K424" s="1"/>
+      <c r="J424" s="33"/>
+      <c r="K424" s="33"/>
       <c r="L424" s="2"/>
       <c r="M424" s="1"/>
       <c r="N424" s="1"/>
@@ -12513,8 +12532,8 @@
       <c r="G425" s="1"/>
       <c r="H425" s="1"/>
       <c r="I425" s="1"/>
-      <c r="J425" s="1"/>
-      <c r="K425" s="1"/>
+      <c r="J425" s="33"/>
+      <c r="K425" s="33"/>
       <c r="L425" s="2"/>
       <c r="M425" s="1"/>
       <c r="N425" s="1"/>
@@ -12541,8 +12560,8 @@
       <c r="G426" s="1"/>
       <c r="H426" s="1"/>
       <c r="I426" s="1"/>
-      <c r="J426" s="1"/>
-      <c r="K426" s="1"/>
+      <c r="J426" s="33"/>
+      <c r="K426" s="33"/>
       <c r="L426" s="2"/>
       <c r="M426" s="1"/>
       <c r="N426" s="1"/>
@@ -12569,8 +12588,8 @@
       <c r="G427" s="1"/>
       <c r="H427" s="1"/>
       <c r="I427" s="1"/>
-      <c r="J427" s="1"/>
-      <c r="K427" s="1"/>
+      <c r="J427" s="33"/>
+      <c r="K427" s="33"/>
       <c r="L427" s="2"/>
       <c r="M427" s="1"/>
       <c r="N427" s="1"/>
@@ -12597,8 +12616,8 @@
       <c r="G428" s="1"/>
       <c r="H428" s="1"/>
       <c r="I428" s="1"/>
-      <c r="J428" s="1"/>
-      <c r="K428" s="1"/>
+      <c r="J428" s="33"/>
+      <c r="K428" s="33"/>
       <c r="L428" s="2"/>
       <c r="M428" s="1"/>
       <c r="N428" s="1"/>
@@ -12625,8 +12644,8 @@
       <c r="G429" s="1"/>
       <c r="H429" s="1"/>
       <c r="I429" s="1"/>
-      <c r="J429" s="1"/>
-      <c r="K429" s="1"/>
+      <c r="J429" s="33"/>
+      <c r="K429" s="33"/>
       <c r="L429" s="2"/>
       <c r="M429" s="1"/>
       <c r="N429" s="1"/>
@@ -12653,8 +12672,8 @@
       <c r="G430" s="1"/>
       <c r="H430" s="1"/>
       <c r="I430" s="1"/>
-      <c r="J430" s="1"/>
-      <c r="K430" s="1"/>
+      <c r="J430" s="33"/>
+      <c r="K430" s="33"/>
       <c r="L430" s="2"/>
       <c r="M430" s="1"/>
       <c r="N430" s="1"/>
@@ -12681,8 +12700,8 @@
       <c r="G431" s="1"/>
       <c r="H431" s="1"/>
       <c r="I431" s="1"/>
-      <c r="J431" s="1"/>
-      <c r="K431" s="1"/>
+      <c r="J431" s="33"/>
+      <c r="K431" s="33"/>
       <c r="L431" s="2"/>
       <c r="M431" s="1"/>
       <c r="N431" s="1"/>
@@ -12709,8 +12728,8 @@
       <c r="G432" s="1"/>
       <c r="H432" s="1"/>
       <c r="I432" s="1"/>
-      <c r="J432" s="1"/>
-      <c r="K432" s="1"/>
+      <c r="J432" s="33"/>
+      <c r="K432" s="33"/>
       <c r="L432" s="2"/>
       <c r="M432" s="1"/>
       <c r="N432" s="1"/>
@@ -12737,8 +12756,8 @@
       <c r="G433" s="1"/>
       <c r="H433" s="1"/>
       <c r="I433" s="1"/>
-      <c r="J433" s="1"/>
-      <c r="K433" s="1"/>
+      <c r="J433" s="33"/>
+      <c r="K433" s="33"/>
       <c r="L433" s="2"/>
       <c r="M433" s="1"/>
       <c r="N433" s="1"/>
@@ -12765,8 +12784,8 @@
       <c r="G434" s="1"/>
       <c r="H434" s="1"/>
       <c r="I434" s="1"/>
-      <c r="J434" s="1"/>
-      <c r="K434" s="1"/>
+      <c r="J434" s="33"/>
+      <c r="K434" s="33"/>
       <c r="L434" s="2"/>
       <c r="M434" s="1"/>
       <c r="N434" s="1"/>
@@ -12793,8 +12812,8 @@
       <c r="G435" s="1"/>
       <c r="H435" s="1"/>
       <c r="I435" s="1"/>
-      <c r="J435" s="1"/>
-      <c r="K435" s="1"/>
+      <c r="J435" s="33"/>
+      <c r="K435" s="33"/>
       <c r="L435" s="2"/>
       <c r="M435" s="1"/>
       <c r="N435" s="1"/>
@@ -12821,8 +12840,8 @@
       <c r="G436" s="1"/>
       <c r="H436" s="1"/>
       <c r="I436" s="1"/>
-      <c r="J436" s="1"/>
-      <c r="K436" s="1"/>
+      <c r="J436" s="33"/>
+      <c r="K436" s="33"/>
       <c r="L436" s="2"/>
       <c r="M436" s="1"/>
       <c r="N436" s="1"/>
@@ -12849,8 +12868,8 @@
       <c r="G437" s="1"/>
       <c r="H437" s="1"/>
       <c r="I437" s="1"/>
-      <c r="J437" s="1"/>
-      <c r="K437" s="1"/>
+      <c r="J437" s="33"/>
+      <c r="K437" s="33"/>
       <c r="L437" s="2"/>
       <c r="M437" s="1"/>
       <c r="N437" s="1"/>
@@ -12877,8 +12896,8 @@
       <c r="G438" s="1"/>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
-      <c r="J438" s="1"/>
-      <c r="K438" s="1"/>
+      <c r="J438" s="33"/>
+      <c r="K438" s="33"/>
       <c r="L438" s="2"/>
       <c r="M438" s="1"/>
       <c r="N438" s="1"/>
@@ -12905,8 +12924,8 @@
       <c r="G439" s="1"/>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
-      <c r="J439" s="1"/>
-      <c r="K439" s="1"/>
+      <c r="J439" s="33"/>
+      <c r="K439" s="33"/>
       <c r="L439" s="2"/>
       <c r="M439" s="1"/>
       <c r="N439" s="1"/>
@@ -12933,8 +12952,8 @@
       <c r="G440" s="1"/>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
-      <c r="J440" s="1"/>
-      <c r="K440" s="1"/>
+      <c r="J440" s="33"/>
+      <c r="K440" s="33"/>
       <c r="L440" s="2"/>
       <c r="M440" s="1"/>
       <c r="N440" s="1"/>
@@ -12961,8 +12980,8 @@
       <c r="G441" s="1"/>
       <c r="H441" s="1"/>
       <c r="I441" s="1"/>
-      <c r="J441" s="1"/>
-      <c r="K441" s="1"/>
+      <c r="J441" s="33"/>
+      <c r="K441" s="33"/>
       <c r="L441" s="2"/>
       <c r="M441" s="1"/>
       <c r="N441" s="1"/>
@@ -12989,8 +13008,8 @@
       <c r="G442" s="1"/>
       <c r="H442" s="1"/>
       <c r="I442" s="1"/>
-      <c r="J442" s="1"/>
-      <c r="K442" s="1"/>
+      <c r="J442" s="33"/>
+      <c r="K442" s="33"/>
       <c r="L442" s="2"/>
       <c r="M442" s="1"/>
       <c r="N442" s="1"/>
@@ -13017,8 +13036,8 @@
       <c r="G443" s="1"/>
       <c r="H443" s="1"/>
       <c r="I443" s="1"/>
-      <c r="J443" s="1"/>
-      <c r="K443" s="1"/>
+      <c r="J443" s="33"/>
+      <c r="K443" s="33"/>
       <c r="L443" s="2"/>
       <c r="M443" s="1"/>
       <c r="N443" s="1"/>
@@ -13045,8 +13064,8 @@
       <c r="G444" s="1"/>
       <c r="H444" s="1"/>
       <c r="I444" s="1"/>
-      <c r="J444" s="1"/>
-      <c r="K444" s="1"/>
+      <c r="J444" s="33"/>
+      <c r="K444" s="33"/>
       <c r="L444" s="2"/>
       <c r="M444" s="1"/>
       <c r="N444" s="1"/>
@@ -13073,8 +13092,8 @@
       <c r="G445" s="1"/>
       <c r="H445" s="1"/>
       <c r="I445" s="1"/>
-      <c r="J445" s="1"/>
-      <c r="K445" s="1"/>
+      <c r="J445" s="33"/>
+      <c r="K445" s="33"/>
       <c r="L445" s="2"/>
       <c r="M445" s="1"/>
       <c r="N445" s="1"/>
@@ -13101,8 +13120,8 @@
       <c r="G446" s="1"/>
       <c r="H446" s="1"/>
       <c r="I446" s="1"/>
-      <c r="J446" s="1"/>
-      <c r="K446" s="1"/>
+      <c r="J446" s="33"/>
+      <c r="K446" s="33"/>
       <c r="L446" s="2"/>
       <c r="M446" s="1"/>
       <c r="N446" s="1"/>
@@ -13129,8 +13148,8 @@
       <c r="G447" s="1"/>
       <c r="H447" s="1"/>
       <c r="I447" s="1"/>
-      <c r="J447" s="1"/>
-      <c r="K447" s="1"/>
+      <c r="J447" s="33"/>
+      <c r="K447" s="33"/>
       <c r="L447" s="2"/>
       <c r="M447" s="1"/>
       <c r="N447" s="1"/>
@@ -13157,8 +13176,8 @@
       <c r="G448" s="1"/>
       <c r="H448" s="1"/>
       <c r="I448" s="1"/>
-      <c r="J448" s="1"/>
-      <c r="K448" s="1"/>
+      <c r="J448" s="33"/>
+      <c r="K448" s="33"/>
       <c r="L448" s="2"/>
       <c r="M448" s="1"/>
       <c r="N448" s="1"/>
@@ -13185,8 +13204,8 @@
       <c r="G449" s="1"/>
       <c r="H449" s="1"/>
       <c r="I449" s="1"/>
-      <c r="J449" s="1"/>
-      <c r="K449" s="1"/>
+      <c r="J449" s="33"/>
+      <c r="K449" s="33"/>
       <c r="L449" s="2"/>
       <c r="M449" s="1"/>
       <c r="N449" s="1"/>
@@ -13213,8 +13232,8 @@
       <c r="G450" s="1"/>
       <c r="H450" s="1"/>
       <c r="I450" s="1"/>
-      <c r="J450" s="1"/>
-      <c r="K450" s="1"/>
+      <c r="J450" s="33"/>
+      <c r="K450" s="33"/>
       <c r="L450" s="2"/>
       <c r="M450" s="1"/>
       <c r="N450" s="1"/>
@@ -13241,8 +13260,8 @@
       <c r="G451" s="1"/>
       <c r="H451" s="1"/>
       <c r="I451" s="1"/>
-      <c r="J451" s="1"/>
-      <c r="K451" s="1"/>
+      <c r="J451" s="33"/>
+      <c r="K451" s="33"/>
       <c r="L451" s="2"/>
       <c r="M451" s="1"/>
       <c r="N451" s="1"/>
@@ -13269,8 +13288,8 @@
       <c r="G452" s="1"/>
       <c r="H452" s="1"/>
       <c r="I452" s="1"/>
-      <c r="J452" s="1"/>
-      <c r="K452" s="1"/>
+      <c r="J452" s="33"/>
+      <c r="K452" s="33"/>
       <c r="L452" s="2"/>
       <c r="M452" s="1"/>
       <c r="N452" s="1"/>
@@ -13297,8 +13316,8 @@
       <c r="G453" s="1"/>
       <c r="H453" s="1"/>
       <c r="I453" s="1"/>
-      <c r="J453" s="1"/>
-      <c r="K453" s="1"/>
+      <c r="J453" s="33"/>
+      <c r="K453" s="33"/>
       <c r="L453" s="2"/>
       <c r="M453" s="1"/>
       <c r="N453" s="1"/>
@@ -13325,8 +13344,8 @@
       <c r="G454" s="1"/>
       <c r="H454" s="1"/>
       <c r="I454" s="1"/>
-      <c r="J454" s="1"/>
-      <c r="K454" s="1"/>
+      <c r="J454" s="33"/>
+      <c r="K454" s="33"/>
       <c r="L454" s="2"/>
       <c r="M454" s="1"/>
       <c r="N454" s="1"/>
@@ -13353,8 +13372,8 @@
       <c r="G455" s="1"/>
       <c r="H455" s="1"/>
       <c r="I455" s="1"/>
-      <c r="J455" s="1"/>
-      <c r="K455" s="1"/>
+      <c r="J455" s="33"/>
+      <c r="K455" s="33"/>
       <c r="L455" s="2"/>
       <c r="M455" s="1"/>
       <c r="N455" s="1"/>
@@ -13381,8 +13400,8 @@
       <c r="G456" s="1"/>
       <c r="H456" s="1"/>
       <c r="I456" s="1"/>
-      <c r="J456" s="1"/>
-      <c r="K456" s="1"/>
+      <c r="J456" s="33"/>
+      <c r="K456" s="33"/>
       <c r="L456" s="2"/>
       <c r="M456" s="1"/>
       <c r="N456" s="1"/>
@@ -13409,8 +13428,8 @@
       <c r="G457" s="1"/>
       <c r="H457" s="1"/>
       <c r="I457" s="1"/>
-      <c r="J457" s="1"/>
-      <c r="K457" s="1"/>
+      <c r="J457" s="33"/>
+      <c r="K457" s="33"/>
       <c r="L457" s="2"/>
       <c r="M457" s="1"/>
       <c r="N457" s="1"/>
@@ -13437,8 +13456,8 @@
       <c r="G458" s="1"/>
       <c r="H458" s="1"/>
       <c r="I458" s="1"/>
-      <c r="J458" s="1"/>
-      <c r="K458" s="1"/>
+      <c r="J458" s="33"/>
+      <c r="K458" s="33"/>
       <c r="L458" s="2"/>
       <c r="M458" s="1"/>
       <c r="N458" s="1"/>
@@ -13465,8 +13484,8 @@
       <c r="G459" s="1"/>
       <c r="H459" s="1"/>
       <c r="I459" s="1"/>
-      <c r="J459" s="1"/>
-      <c r="K459" s="1"/>
+      <c r="J459" s="33"/>
+      <c r="K459" s="33"/>
       <c r="L459" s="2"/>
       <c r="M459" s="1"/>
       <c r="N459" s="1"/>
@@ -13493,8 +13512,8 @@
       <c r="G460" s="1"/>
       <c r="H460" s="1"/>
       <c r="I460" s="1"/>
-      <c r="J460" s="1"/>
-      <c r="K460" s="1"/>
+      <c r="J460" s="33"/>
+      <c r="K460" s="33"/>
       <c r="L460" s="2"/>
       <c r="M460" s="1"/>
       <c r="N460" s="1"/>
@@ -13521,8 +13540,8 @@
       <c r="G461" s="1"/>
       <c r="H461" s="1"/>
       <c r="I461" s="1"/>
-      <c r="J461" s="1"/>
-      <c r="K461" s="1"/>
+      <c r="J461" s="33"/>
+      <c r="K461" s="33"/>
       <c r="L461" s="2"/>
       <c r="M461" s="1"/>
       <c r="N461" s="1"/>
@@ -13549,8 +13568,8 @@
       <c r="G462" s="1"/>
       <c r="H462" s="1"/>
       <c r="I462" s="1"/>
-      <c r="J462" s="1"/>
-      <c r="K462" s="1"/>
+      <c r="J462" s="33"/>
+      <c r="K462" s="33"/>
       <c r="L462" s="2"/>
       <c r="M462" s="1"/>
       <c r="N462" s="1"/>
@@ -13577,8 +13596,8 @@
       <c r="G463" s="1"/>
       <c r="H463" s="1"/>
       <c r="I463" s="1"/>
-      <c r="J463" s="1"/>
-      <c r="K463" s="1"/>
+      <c r="J463" s="33"/>
+      <c r="K463" s="33"/>
       <c r="L463" s="2"/>
       <c r="M463" s="1"/>
       <c r="N463" s="1"/>
@@ -13605,8 +13624,8 @@
       <c r="G464" s="1"/>
       <c r="H464" s="1"/>
       <c r="I464" s="1"/>
-      <c r="J464" s="1"/>
-      <c r="K464" s="1"/>
+      <c r="J464" s="33"/>
+      <c r="K464" s="33"/>
       <c r="L464" s="2"/>
       <c r="M464" s="1"/>
       <c r="N464" s="1"/>
@@ -13633,8 +13652,8 @@
       <c r="G465" s="1"/>
       <c r="H465" s="1"/>
       <c r="I465" s="1"/>
-      <c r="J465" s="1"/>
-      <c r="K465" s="1"/>
+      <c r="J465" s="33"/>
+      <c r="K465" s="33"/>
       <c r="L465" s="2"/>
       <c r="M465" s="1"/>
       <c r="N465" s="1"/>
@@ -13661,8 +13680,8 @@
       <c r="G466" s="1"/>
       <c r="H466" s="1"/>
       <c r="I466" s="1"/>
-      <c r="J466" s="1"/>
-      <c r="K466" s="1"/>
+      <c r="J466" s="33"/>
+      <c r="K466" s="33"/>
       <c r="L466" s="2"/>
       <c r="M466" s="1"/>
       <c r="N466" s="1"/>
@@ -13689,8 +13708,8 @@
       <c r="G467" s="1"/>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
-      <c r="J467" s="1"/>
-      <c r="K467" s="1"/>
+      <c r="J467" s="33"/>
+      <c r="K467" s="33"/>
       <c r="L467" s="2"/>
       <c r="M467" s="1"/>
       <c r="N467" s="1"/>
@@ -13717,8 +13736,8 @@
       <c r="G468" s="1"/>
       <c r="H468" s="1"/>
       <c r="I468" s="1"/>
-      <c r="J468" s="1"/>
-      <c r="K468" s="1"/>
+      <c r="J468" s="33"/>
+      <c r="K468" s="33"/>
       <c r="L468" s="2"/>
       <c r="M468" s="1"/>
       <c r="N468" s="1"/>
@@ -13745,8 +13764,8 @@
       <c r="G469" s="1"/>
       <c r="H469" s="1"/>
       <c r="I469" s="1"/>
-      <c r="J469" s="1"/>
-      <c r="K469" s="1"/>
+      <c r="J469" s="33"/>
+      <c r="K469" s="33"/>
       <c r="L469" s="2"/>
       <c r="M469" s="1"/>
       <c r="N469" s="1"/>
@@ -13773,8 +13792,8 @@
       <c r="G470" s="1"/>
       <c r="H470" s="1"/>
       <c r="I470" s="1"/>
-      <c r="J470" s="1"/>
-      <c r="K470" s="1"/>
+      <c r="J470" s="33"/>
+      <c r="K470" s="33"/>
       <c r="L470" s="2"/>
       <c r="M470" s="1"/>
       <c r="N470" s="1"/>
@@ -13801,8 +13820,8 @@
       <c r="G471" s="1"/>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
-      <c r="J471" s="1"/>
-      <c r="K471" s="1"/>
+      <c r="J471" s="33"/>
+      <c r="K471" s="33"/>
       <c r="L471" s="2"/>
       <c r="M471" s="1"/>
       <c r="N471" s="1"/>
@@ -13829,8 +13848,8 @@
       <c r="G472" s="1"/>
       <c r="H472" s="1"/>
       <c r="I472" s="1"/>
-      <c r="J472" s="1"/>
-      <c r="K472" s="1"/>
+      <c r="J472" s="33"/>
+      <c r="K472" s="33"/>
       <c r="L472" s="2"/>
       <c r="M472" s="1"/>
       <c r="N472" s="1"/>
@@ -13857,8 +13876,8 @@
       <c r="G473" s="1"/>
       <c r="H473" s="1"/>
       <c r="I473" s="1"/>
-      <c r="J473" s="1"/>
-      <c r="K473" s="1"/>
+      <c r="J473" s="33"/>
+      <c r="K473" s="33"/>
       <c r="L473" s="2"/>
       <c r="M473" s="1"/>
       <c r="N473" s="1"/>
@@ -13885,8 +13904,8 @@
       <c r="G474" s="1"/>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
-      <c r="J474" s="1"/>
-      <c r="K474" s="1"/>
+      <c r="J474" s="33"/>
+      <c r="K474" s="33"/>
       <c r="L474" s="2"/>
       <c r="M474" s="1"/>
       <c r="N474" s="1"/>
@@ -13913,8 +13932,8 @@
       <c r="G475" s="1"/>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
-      <c r="J475" s="1"/>
-      <c r="K475" s="1"/>
+      <c r="J475" s="33"/>
+      <c r="K475" s="33"/>
       <c r="L475" s="2"/>
       <c r="M475" s="1"/>
       <c r="N475" s="1"/>
@@ -13941,8 +13960,8 @@
       <c r="G476" s="1"/>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
-      <c r="J476" s="1"/>
-      <c r="K476" s="1"/>
+      <c r="J476" s="33"/>
+      <c r="K476" s="33"/>
       <c r="L476" s="2"/>
       <c r="M476" s="1"/>
       <c r="N476" s="1"/>
@@ -13969,8 +13988,8 @@
       <c r="G477" s="1"/>
       <c r="H477" s="1"/>
       <c r="I477" s="1"/>
-      <c r="J477" s="1"/>
-      <c r="K477" s="1"/>
+      <c r="J477" s="33"/>
+      <c r="K477" s="33"/>
       <c r="L477" s="2"/>
       <c r="M477" s="1"/>
       <c r="N477" s="1"/>
@@ -13997,8 +14016,8 @@
       <c r="G478" s="1"/>
       <c r="H478" s="1"/>
       <c r="I478" s="1"/>
-      <c r="J478" s="1"/>
-      <c r="K478" s="1"/>
+      <c r="J478" s="33"/>
+      <c r="K478" s="33"/>
       <c r="L478" s="2"/>
       <c r="M478" s="1"/>
       <c r="N478" s="1"/>
@@ -14025,8 +14044,8 @@
       <c r="G479" s="1"/>
       <c r="H479" s="1"/>
       <c r="I479" s="1"/>
-      <c r="J479" s="1"/>
-      <c r="K479" s="1"/>
+      <c r="J479" s="33"/>
+      <c r="K479" s="33"/>
       <c r="L479" s="2"/>
       <c r="M479" s="1"/>
       <c r="N479" s="1"/>
@@ -14053,8 +14072,8 @@
       <c r="G480" s="1"/>
       <c r="H480" s="1"/>
       <c r="I480" s="1"/>
-      <c r="J480" s="1"/>
-      <c r="K480" s="1"/>
+      <c r="J480" s="33"/>
+      <c r="K480" s="33"/>
       <c r="L480" s="2"/>
       <c r="M480" s="1"/>
       <c r="N480" s="1"/>
@@ -14081,8 +14100,8 @@
       <c r="G481" s="1"/>
       <c r="H481" s="1"/>
       <c r="I481" s="1"/>
-      <c r="J481" s="1"/>
-      <c r="K481" s="1"/>
+      <c r="J481" s="33"/>
+      <c r="K481" s="33"/>
       <c r="L481" s="2"/>
       <c r="M481" s="1"/>
       <c r="N481" s="1"/>
@@ -14109,8 +14128,8 @@
       <c r="G482" s="1"/>
       <c r="H482" s="1"/>
       <c r="I482" s="1"/>
-      <c r="J482" s="1"/>
-      <c r="K482" s="1"/>
+      <c r="J482" s="33"/>
+      <c r="K482" s="33"/>
       <c r="L482" s="2"/>
       <c r="M482" s="1"/>
       <c r="N482" s="1"/>
@@ -14137,8 +14156,8 @@
       <c r="G483" s="1"/>
       <c r="H483" s="1"/>
       <c r="I483" s="1"/>
-      <c r="J483" s="1"/>
-      <c r="K483" s="1"/>
+      <c r="J483" s="33"/>
+      <c r="K483" s="33"/>
       <c r="L483" s="2"/>
       <c r="M483" s="1"/>
       <c r="N483" s="1"/>
@@ -14165,8 +14184,8 @@
       <c r="G484" s="1"/>
       <c r="H484" s="1"/>
       <c r="I484" s="1"/>
-      <c r="J484" s="1"/>
-      <c r="K484" s="1"/>
+      <c r="J484" s="33"/>
+      <c r="K484" s="33"/>
       <c r="L484" s="2"/>
       <c r="M484" s="1"/>
       <c r="N484" s="1"/>
@@ -14193,8 +14212,8 @@
       <c r="G485" s="1"/>
       <c r="H485" s="1"/>
       <c r="I485" s="1"/>
-      <c r="J485" s="1"/>
-      <c r="K485" s="1"/>
+      <c r="J485" s="33"/>
+      <c r="K485" s="33"/>
       <c r="L485" s="2"/>
       <c r="M485" s="1"/>
       <c r="N485" s="1"/>
@@ -14221,8 +14240,8 @@
       <c r="G486" s="1"/>
       <c r="H486" s="1"/>
       <c r="I486" s="1"/>
-      <c r="J486" s="1"/>
-      <c r="K486" s="1"/>
+      <c r="J486" s="33"/>
+      <c r="K486" s="33"/>
       <c r="L486" s="2"/>
       <c r="M486" s="1"/>
       <c r="N486" s="1"/>
@@ -14249,8 +14268,8 @@
       <c r="G487" s="1"/>
       <c r="H487" s="1"/>
       <c r="I487" s="1"/>
-      <c r="J487" s="1"/>
-      <c r="K487" s="1"/>
+      <c r="J487" s="33"/>
+      <c r="K487" s="33"/>
       <c r="L487" s="2"/>
       <c r="M487" s="1"/>
       <c r="N487" s="1"/>
@@ -14277,8 +14296,8 @@
       <c r="G488" s="1"/>
       <c r="H488" s="1"/>
       <c r="I488" s="1"/>
-      <c r="J488" s="1"/>
-      <c r="K488" s="1"/>
+      <c r="J488" s="33"/>
+      <c r="K488" s="33"/>
       <c r="L488" s="2"/>
       <c r="M488" s="1"/>
       <c r="N488" s="1"/>
@@ -14305,8 +14324,8 @@
       <c r="G489" s="1"/>
       <c r="H489" s="1"/>
       <c r="I489" s="1"/>
-      <c r="J489" s="1"/>
-      <c r="K489" s="1"/>
+      <c r="J489" s="33"/>
+      <c r="K489" s="33"/>
       <c r="L489" s="2"/>
       <c r="M489" s="1"/>
       <c r="N489" s="1"/>
@@ -14333,8 +14352,8 @@
       <c r="G490" s="1"/>
       <c r="H490" s="1"/>
       <c r="I490" s="1"/>
-      <c r="J490" s="1"/>
-      <c r="K490" s="1"/>
+      <c r="J490" s="33"/>
+      <c r="K490" s="33"/>
       <c r="L490" s="2"/>
       <c r="M490" s="1"/>
       <c r="N490" s="1"/>
@@ -14361,8 +14380,8 @@
       <c r="G491" s="1"/>
       <c r="H491" s="1"/>
       <c r="I491" s="1"/>
-      <c r="J491" s="1"/>
-      <c r="K491" s="1"/>
+      <c r="J491" s="33"/>
+      <c r="K491" s="33"/>
       <c r="L491" s="2"/>
       <c r="M491" s="1"/>
       <c r="N491" s="1"/>
@@ -14389,8 +14408,8 @@
       <c r="G492" s="1"/>
       <c r="H492" s="1"/>
       <c r="I492" s="1"/>
-      <c r="J492" s="1"/>
-      <c r="K492" s="1"/>
+      <c r="J492" s="33"/>
+      <c r="K492" s="33"/>
       <c r="L492" s="2"/>
       <c r="M492" s="1"/>
       <c r="N492" s="1"/>
@@ -14417,8 +14436,8 @@
       <c r="G493" s="1"/>
       <c r="H493" s="1"/>
       <c r="I493" s="1"/>
-      <c r="J493" s="1"/>
-      <c r="K493" s="1"/>
+      <c r="J493" s="33"/>
+      <c r="K493" s="33"/>
       <c r="L493" s="2"/>
       <c r="M493" s="1"/>
       <c r="N493" s="1"/>
@@ -14445,8 +14464,8 @@
       <c r="G494" s="1"/>
       <c r="H494" s="1"/>
       <c r="I494" s="1"/>
-      <c r="J494" s="1"/>
-      <c r="K494" s="1"/>
+      <c r="J494" s="33"/>
+      <c r="K494" s="33"/>
       <c r="L494" s="2"/>
       <c r="M494" s="1"/>
       <c r="N494" s="1"/>
@@ -14473,8 +14492,8 @@
       <c r="G495" s="1"/>
       <c r="H495" s="1"/>
       <c r="I495" s="1"/>
-      <c r="J495" s="1"/>
-      <c r="K495" s="1"/>
+      <c r="J495" s="33"/>
+      <c r="K495" s="33"/>
       <c r="L495" s="2"/>
       <c r="M495" s="1"/>
       <c r="N495" s="1"/>
@@ -14501,8 +14520,8 @@
       <c r="G496" s="1"/>
       <c r="H496" s="1"/>
       <c r="I496" s="1"/>
-      <c r="J496" s="1"/>
-      <c r="K496" s="1"/>
+      <c r="J496" s="33"/>
+      <c r="K496" s="33"/>
       <c r="L496" s="2"/>
       <c r="M496" s="1"/>
       <c r="N496" s="1"/>
@@ -14529,8 +14548,8 @@
       <c r="G497" s="1"/>
       <c r="H497" s="1"/>
       <c r="I497" s="1"/>
-      <c r="J497" s="1"/>
-      <c r="K497" s="1"/>
+      <c r="J497" s="33"/>
+      <c r="K497" s="33"/>
       <c r="L497" s="2"/>
       <c r="M497" s="1"/>
       <c r="N497" s="1"/>
@@ -14557,8 +14576,8 @@
       <c r="G498" s="1"/>
       <c r="H498" s="1"/>
       <c r="I498" s="1"/>
-      <c r="J498" s="1"/>
-      <c r="K498" s="1"/>
+      <c r="J498" s="33"/>
+      <c r="K498" s="33"/>
       <c r="L498" s="2"/>
       <c r="M498" s="1"/>
       <c r="N498" s="1"/>
@@ -14585,8 +14604,8 @@
       <c r="G499" s="1"/>
       <c r="H499" s="1"/>
       <c r="I499" s="1"/>
-      <c r="J499" s="1"/>
-      <c r="K499" s="1"/>
+      <c r="J499" s="33"/>
+      <c r="K499" s="33"/>
       <c r="L499" s="2"/>
       <c r="M499" s="1"/>
       <c r="N499" s="1"/>
@@ -14613,8 +14632,8 @@
       <c r="G500" s="1"/>
       <c r="H500" s="1"/>
       <c r="I500" s="1"/>
-      <c r="J500" s="1"/>
-      <c r="K500" s="1"/>
+      <c r="J500" s="33"/>
+      <c r="K500" s="33"/>
       <c r="L500" s="2"/>
       <c r="M500" s="1"/>
       <c r="N500" s="1"/>
@@ -14641,8 +14660,8 @@
       <c r="G501" s="1"/>
       <c r="H501" s="1"/>
       <c r="I501" s="1"/>
-      <c r="J501" s="1"/>
-      <c r="K501" s="1"/>
+      <c r="J501" s="33"/>
+      <c r="K501" s="33"/>
       <c r="L501" s="2"/>
       <c r="M501" s="1"/>
       <c r="N501" s="1"/>
@@ -14669,8 +14688,8 @@
       <c r="G502" s="1"/>
       <c r="H502" s="1"/>
       <c r="I502" s="1"/>
-      <c r="J502" s="1"/>
-      <c r="K502" s="1"/>
+      <c r="J502" s="33"/>
+      <c r="K502" s="33"/>
       <c r="L502" s="2"/>
       <c r="M502" s="1"/>
       <c r="N502" s="1"/>
@@ -14697,8 +14716,8 @@
       <c r="G503" s="1"/>
       <c r="H503" s="1"/>
       <c r="I503" s="1"/>
-      <c r="J503" s="1"/>
-      <c r="K503" s="1"/>
+      <c r="J503" s="33"/>
+      <c r="K503" s="33"/>
       <c r="L503" s="2"/>
       <c r="M503" s="1"/>
       <c r="N503" s="1"/>
@@ -14725,8 +14744,8 @@
       <c r="G504" s="1"/>
       <c r="H504" s="1"/>
       <c r="I504" s="1"/>
-      <c r="J504" s="1"/>
-      <c r="K504" s="1"/>
+      <c r="J504" s="33"/>
+      <c r="K504" s="33"/>
       <c r="L504" s="2"/>
       <c r="M504" s="1"/>
       <c r="N504" s="1"/>
@@ -14753,8 +14772,8 @@
       <c r="G505" s="1"/>
       <c r="H505" s="1"/>
       <c r="I505" s="1"/>
-      <c r="J505" s="1"/>
-      <c r="K505" s="1"/>
+      <c r="J505" s="33"/>
+      <c r="K505" s="33"/>
       <c r="L505" s="2"/>
       <c r="M505" s="1"/>
       <c r="N505" s="1"/>
@@ -14781,8 +14800,8 @@
       <c r="G506" s="1"/>
       <c r="H506" s="1"/>
       <c r="I506" s="1"/>
-      <c r="J506" s="1"/>
-      <c r="K506" s="1"/>
+      <c r="J506" s="33"/>
+      <c r="K506" s="33"/>
       <c r="L506" s="2"/>
       <c r="M506" s="1"/>
       <c r="N506" s="1"/>
@@ -14809,8 +14828,8 @@
       <c r="G507" s="1"/>
       <c r="H507" s="1"/>
       <c r="I507" s="1"/>
-      <c r="J507" s="1"/>
-      <c r="K507" s="1"/>
+      <c r="J507" s="33"/>
+      <c r="K507" s="33"/>
       <c r="L507" s="2"/>
       <c r="M507" s="1"/>
       <c r="N507" s="1"/>
@@ -14837,8 +14856,8 @@
       <c r="G508" s="1"/>
       <c r="H508" s="1"/>
       <c r="I508" s="1"/>
-      <c r="J508" s="1"/>
-      <c r="K508" s="1"/>
+      <c r="J508" s="33"/>
+      <c r="K508" s="33"/>
       <c r="L508" s="2"/>
       <c r="M508" s="1"/>
       <c r="N508" s="1"/>
@@ -14865,8 +14884,8 @@
       <c r="G509" s="1"/>
       <c r="H509" s="1"/>
       <c r="I509" s="1"/>
-      <c r="J509" s="1"/>
-      <c r="K509" s="1"/>
+      <c r="J509" s="33"/>
+      <c r="K509" s="33"/>
       <c r="L509" s="2"/>
       <c r="M509" s="1"/>
       <c r="N509" s="1"/>
@@ -14893,8 +14912,8 @@
       <c r="G510" s="1"/>
       <c r="H510" s="1"/>
       <c r="I510" s="1"/>
-      <c r="J510" s="1"/>
-      <c r="K510" s="1"/>
+      <c r="J510" s="33"/>
+      <c r="K510" s="33"/>
       <c r="L510" s="2"/>
       <c r="M510" s="1"/>
       <c r="N510" s="1"/>
@@ -14921,8 +14940,8 @@
       <c r="G511" s="1"/>
       <c r="H511" s="1"/>
       <c r="I511" s="1"/>
-      <c r="J511" s="1"/>
-      <c r="K511" s="1"/>
+      <c r="J511" s="33"/>
+      <c r="K511" s="33"/>
       <c r="L511" s="2"/>
       <c r="M511" s="1"/>
       <c r="N511" s="1"/>
@@ -14949,8 +14968,8 @@
       <c r="G512" s="1"/>
       <c r="H512" s="1"/>
       <c r="I512" s="1"/>
-      <c r="J512" s="1"/>
-      <c r="K512" s="1"/>
+      <c r="J512" s="33"/>
+      <c r="K512" s="33"/>
       <c r="L512" s="2"/>
       <c r="M512" s="1"/>
       <c r="N512" s="1"/>
@@ -14977,8 +14996,8 @@
       <c r="G513" s="1"/>
       <c r="H513" s="1"/>
       <c r="I513" s="1"/>
-      <c r="J513" s="1"/>
-      <c r="K513" s="1"/>
+      <c r="J513" s="33"/>
+      <c r="K513" s="33"/>
       <c r="L513" s="2"/>
       <c r="M513" s="1"/>
       <c r="N513" s="1"/>
@@ -15005,8 +15024,8 @@
       <c r="G514" s="1"/>
       <c r="H514" s="1"/>
       <c r="I514" s="1"/>
-      <c r="J514" s="1"/>
-      <c r="K514" s="1"/>
+      <c r="J514" s="33"/>
+      <c r="K514" s="33"/>
       <c r="L514" s="2"/>
       <c r="M514" s="1"/>
       <c r="N514" s="1"/>
@@ -15033,8 +15052,8 @@
       <c r="G515" s="1"/>
       <c r="H515" s="1"/>
       <c r="I515" s="1"/>
-      <c r="J515" s="1"/>
-      <c r="K515" s="1"/>
+      <c r="J515" s="33"/>
+      <c r="K515" s="33"/>
       <c r="L515" s="2"/>
       <c r="M515" s="1"/>
       <c r="N515" s="1"/>
@@ -15061,8 +15080,8 @@
       <c r="G516" s="1"/>
       <c r="H516" s="1"/>
       <c r="I516" s="1"/>
-      <c r="J516" s="1"/>
-      <c r="K516" s="1"/>
+      <c r="J516" s="33"/>
+      <c r="K516" s="33"/>
       <c r="L516" s="2"/>
       <c r="M516" s="1"/>
       <c r="N516" s="1"/>
@@ -15089,8 +15108,8 @@
       <c r="G517" s="1"/>
       <c r="H517" s="1"/>
       <c r="I517" s="1"/>
-      <c r="J517" s="1"/>
-      <c r="K517" s="1"/>
+      <c r="J517" s="33"/>
+      <c r="K517" s="33"/>
       <c r="L517" s="2"/>
       <c r="M517" s="1"/>
       <c r="N517" s="1"/>
@@ -15117,8 +15136,8 @@
       <c r="G518" s="1"/>
       <c r="H518" s="1"/>
       <c r="I518" s="1"/>
-      <c r="J518" s="1"/>
-      <c r="K518" s="1"/>
+      <c r="J518" s="33"/>
+      <c r="K518" s="33"/>
       <c r="L518" s="2"/>
       <c r="M518" s="1"/>
       <c r="N518" s="1"/>
@@ -15145,8 +15164,8 @@
       <c r="G519" s="1"/>
       <c r="H519" s="1"/>
       <c r="I519" s="1"/>
-      <c r="J519" s="1"/>
-      <c r="K519" s="1"/>
+      <c r="J519" s="33"/>
+      <c r="K519" s="33"/>
       <c r="L519" s="2"/>
       <c r="M519" s="1"/>
       <c r="N519" s="1"/>
@@ -15173,8 +15192,8 @@
       <c r="G520" s="1"/>
       <c r="H520" s="1"/>
       <c r="I520" s="1"/>
-      <c r="J520" s="1"/>
-      <c r="K520" s="1"/>
+      <c r="J520" s="33"/>
+      <c r="K520" s="33"/>
       <c r="L520" s="2"/>
       <c r="M520" s="1"/>
       <c r="N520" s="1"/>
@@ -15201,8 +15220,8 @@
       <c r="G521" s="1"/>
       <c r="H521" s="1"/>
       <c r="I521" s="1"/>
-      <c r="J521" s="1"/>
-      <c r="K521" s="1"/>
+      <c r="J521" s="33"/>
+      <c r="K521" s="33"/>
       <c r="L521" s="2"/>
       <c r="M521" s="1"/>
       <c r="N521" s="1"/>
@@ -15229,8 +15248,8 @@
       <c r="G522" s="1"/>
       <c r="H522" s="1"/>
       <c r="I522" s="1"/>
-      <c r="J522" s="1"/>
-      <c r="K522" s="1"/>
+      <c r="J522" s="33"/>
+      <c r="K522" s="33"/>
       <c r="L522" s="2"/>
       <c r="M522" s="1"/>
       <c r="N522" s="1"/>
@@ -15257,8 +15276,8 @@
       <c r="G523" s="1"/>
       <c r="H523" s="1"/>
       <c r="I523" s="1"/>
-      <c r="J523" s="1"/>
-      <c r="K523" s="1"/>
+      <c r="J523" s="33"/>
+      <c r="K523" s="33"/>
       <c r="L523" s="2"/>
       <c r="M523" s="1"/>
       <c r="N523" s="1"/>
@@ -15285,8 +15304,8 @@
       <c r="G524" s="1"/>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
-      <c r="J524" s="1"/>
-      <c r="K524" s="1"/>
+      <c r="J524" s="33"/>
+      <c r="K524" s="33"/>
       <c r="L524" s="2"/>
       <c r="M524" s="1"/>
       <c r="N524" s="1"/>
@@ -15313,8 +15332,8 @@
       <c r="G525" s="1"/>
       <c r="H525" s="1"/>
       <c r="I525" s="1"/>
-      <c r="J525" s="1"/>
-      <c r="K525" s="1"/>
+      <c r="J525" s="33"/>
+      <c r="K525" s="33"/>
       <c r="L525" s="2"/>
       <c r="M525" s="1"/>
       <c r="N525" s="1"/>
@@ -15341,8 +15360,8 @@
       <c r="G526" s="1"/>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
-      <c r="J526" s="1"/>
-      <c r="K526" s="1"/>
+      <c r="J526" s="33"/>
+      <c r="K526" s="33"/>
       <c r="L526" s="2"/>
       <c r="M526" s="1"/>
       <c r="N526" s="1"/>
@@ -15369,8 +15388,8 @@
       <c r="G527" s="1"/>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
-      <c r="J527" s="1"/>
-      <c r="K527" s="1"/>
+      <c r="J527" s="33"/>
+      <c r="K527" s="33"/>
       <c r="L527" s="2"/>
       <c r="M527" s="1"/>
       <c r="N527" s="1"/>
@@ -15397,8 +15416,8 @@
       <c r="G528" s="1"/>
       <c r="H528" s="1"/>
       <c r="I528" s="1"/>
-      <c r="J528" s="1"/>
-      <c r="K528" s="1"/>
+      <c r="J528" s="33"/>
+      <c r="K528" s="33"/>
       <c r="L528" s="2"/>
       <c r="M528" s="1"/>
       <c r="N528" s="1"/>
@@ -15425,8 +15444,8 @@
       <c r="G529" s="1"/>
       <c r="H529" s="1"/>
       <c r="I529" s="1"/>
-      <c r="J529" s="1"/>
-      <c r="K529" s="1"/>
+      <c r="J529" s="33"/>
+      <c r="K529" s="33"/>
       <c r="L529" s="2"/>
       <c r="M529" s="1"/>
       <c r="N529" s="1"/>
@@ -15453,8 +15472,8 @@
       <c r="G530" s="1"/>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
-      <c r="J530" s="1"/>
-      <c r="K530" s="1"/>
+      <c r="J530" s="33"/>
+      <c r="K530" s="33"/>
       <c r="L530" s="2"/>
       <c r="M530" s="1"/>
       <c r="N530" s="1"/>
@@ -15481,8 +15500,8 @@
       <c r="G531" s="1"/>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
-      <c r="J531" s="1"/>
-      <c r="K531" s="1"/>
+      <c r="J531" s="33"/>
+      <c r="K531" s="33"/>
       <c r="L531" s="2"/>
       <c r="M531" s="1"/>
       <c r="N531" s="1"/>
@@ -15509,8 +15528,8 @@
       <c r="G532" s="1"/>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
-      <c r="J532" s="1"/>
-      <c r="K532" s="1"/>
+      <c r="J532" s="33"/>
+      <c r="K532" s="33"/>
       <c r="L532" s="2"/>
       <c r="M532" s="1"/>
       <c r="N532" s="1"/>
@@ -15537,8 +15556,8 @@
       <c r="G533" s="1"/>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
-      <c r="J533" s="1"/>
-      <c r="K533" s="1"/>
+      <c r="J533" s="33"/>
+      <c r="K533" s="33"/>
       <c r="L533" s="2"/>
       <c r="M533" s="1"/>
       <c r="N533" s="1"/>
@@ -15565,8 +15584,8 @@
       <c r="G534" s="1"/>
       <c r="H534" s="1"/>
       <c r="I534" s="1"/>
-      <c r="J534" s="1"/>
-      <c r="K534" s="1"/>
+      <c r="J534" s="33"/>
+      <c r="K534" s="33"/>
       <c r="L534" s="2"/>
       <c r="M534" s="1"/>
       <c r="N534" s="1"/>
@@ -15593,8 +15612,8 @@
       <c r="G535" s="1"/>
       <c r="H535" s="1"/>
       <c r="I535" s="1"/>
-      <c r="J535" s="1"/>
-      <c r="K535" s="1"/>
+      <c r="J535" s="33"/>
+      <c r="K535" s="33"/>
       <c r="L535" s="2"/>
       <c r="M535" s="1"/>
       <c r="N535" s="1"/>
@@ -15621,8 +15640,8 @@
       <c r="G536" s="1"/>
       <c r="H536" s="1"/>
       <c r="I536" s="1"/>
-      <c r="J536" s="1"/>
-      <c r="K536" s="1"/>
+      <c r="J536" s="33"/>
+      <c r="K536" s="33"/>
       <c r="L536" s="2"/>
       <c r="M536" s="1"/>
       <c r="N536" s="1"/>
@@ -15649,8 +15668,8 @@
       <c r="G537" s="1"/>
       <c r="H537" s="1"/>
       <c r="I537" s="1"/>
-      <c r="J537" s="1"/>
-      <c r="K537" s="1"/>
+      <c r="J537" s="33"/>
+      <c r="K537" s="33"/>
       <c r="L537" s="2"/>
       <c r="M537" s="1"/>
       <c r="N537" s="1"/>
@@ -15677,8 +15696,8 @@
       <c r="G538" s="1"/>
       <c r="H538" s="1"/>
       <c r="I538" s="1"/>
-      <c r="J538" s="1"/>
-      <c r="K538" s="1"/>
+      <c r="J538" s="33"/>
+      <c r="K538" s="33"/>
       <c r="L538" s="2"/>
       <c r="M538" s="1"/>
       <c r="N538" s="1"/>
@@ -15705,8 +15724,8 @@
       <c r="G539" s="1"/>
       <c r="H539" s="1"/>
       <c r="I539" s="1"/>
-      <c r="J539" s="1"/>
-      <c r="K539" s="1"/>
+      <c r="J539" s="33"/>
+      <c r="K539" s="33"/>
       <c r="L539" s="2"/>
       <c r="M539" s="1"/>
       <c r="N539" s="1"/>
@@ -15733,8 +15752,8 @@
       <c r="G540" s="1"/>
       <c r="H540" s="1"/>
       <c r="I540" s="1"/>
-      <c r="J540" s="1"/>
-      <c r="K540" s="1"/>
+      <c r="J540" s="33"/>
+      <c r="K540" s="33"/>
       <c r="L540" s="2"/>
       <c r="M540" s="1"/>
       <c r="N540" s="1"/>
@@ -15761,8 +15780,8 @@
       <c r="G541" s="1"/>
       <c r="H541" s="1"/>
       <c r="I541" s="1"/>
-      <c r="J541" s="1"/>
-      <c r="K541" s="1"/>
+      <c r="J541" s="33"/>
+      <c r="K541" s="33"/>
       <c r="L541" s="2"/>
       <c r="M541" s="1"/>
       <c r="N541" s="1"/>
@@ -15789,8 +15808,8 @@
       <c r="G542" s="1"/>
       <c r="H542" s="1"/>
       <c r="I542" s="1"/>
-      <c r="J542" s="1"/>
-      <c r="K542" s="1"/>
+      <c r="J542" s="33"/>
+      <c r="K542" s="33"/>
       <c r="L542" s="2"/>
       <c r="M542" s="1"/>
       <c r="N542" s="1"/>
@@ -15817,8 +15836,8 @@
       <c r="G543" s="1"/>
       <c r="H543" s="1"/>
       <c r="I543" s="1"/>
-      <c r="J543" s="1"/>
-      <c r="K543" s="1"/>
+      <c r="J543" s="33"/>
+      <c r="K543" s="33"/>
       <c r="L543" s="2"/>
       <c r="M543" s="1"/>
       <c r="N543" s="1"/>
@@ -15845,8 +15864,8 @@
       <c r="G544" s="1"/>
       <c r="H544" s="1"/>
       <c r="I544" s="1"/>
-      <c r="J544" s="1"/>
-      <c r="K544" s="1"/>
+      <c r="J544" s="33"/>
+      <c r="K544" s="33"/>
       <c r="L544" s="2"/>
       <c r="M544" s="1"/>
       <c r="N544" s="1"/>
@@ -15873,8 +15892,8 @@
       <c r="G545" s="1"/>
       <c r="H545" s="1"/>
       <c r="I545" s="1"/>
-      <c r="J545" s="1"/>
-      <c r="K545" s="1"/>
+      <c r="J545" s="33"/>
+      <c r="K545" s="33"/>
       <c r="L545" s="2"/>
       <c r="M545" s="1"/>
       <c r="N545" s="1"/>
@@ -15901,8 +15920,8 @@
       <c r="G546" s="1"/>
       <c r="H546" s="1"/>
       <c r="I546" s="1"/>
-      <c r="J546" s="1"/>
-      <c r="K546" s="1"/>
+      <c r="J546" s="33"/>
+      <c r="K546" s="33"/>
       <c r="L546" s="2"/>
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
@@ -15929,8 +15948,8 @@
       <c r="G547" s="1"/>
       <c r="H547" s="1"/>
       <c r="I547" s="1"/>
-      <c r="J547" s="1"/>
-      <c r="K547" s="1"/>
+      <c r="J547" s="33"/>
+      <c r="K547" s="33"/>
       <c r="L547" s="2"/>
       <c r="M547" s="1"/>
       <c r="N547" s="1"/>
@@ -15957,8 +15976,8 @@
       <c r="G548" s="1"/>
       <c r="H548" s="1"/>
       <c r="I548" s="1"/>
-      <c r="J548" s="1"/>
-      <c r="K548" s="1"/>
+      <c r="J548" s="33"/>
+      <c r="K548" s="33"/>
       <c r="L548" s="2"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
@@ -15985,8 +16004,8 @@
       <c r="G549" s="1"/>
       <c r="H549" s="1"/>
       <c r="I549" s="1"/>
-      <c r="J549" s="1"/>
-      <c r="K549" s="1"/>
+      <c r="J549" s="33"/>
+      <c r="K549" s="33"/>
       <c r="L549" s="2"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
@@ -16013,8 +16032,8 @@
       <c r="G550" s="1"/>
       <c r="H550" s="1"/>
       <c r="I550" s="1"/>
-      <c r="J550" s="1"/>
-      <c r="K550" s="1"/>
+      <c r="J550" s="33"/>
+      <c r="K550" s="33"/>
       <c r="L550" s="2"/>
       <c r="M550" s="1"/>
       <c r="N550" s="1"/>
@@ -16041,8 +16060,8 @@
       <c r="G551" s="1"/>
       <c r="H551" s="1"/>
       <c r="I551" s="1"/>
-      <c r="J551" s="1"/>
-      <c r="K551" s="1"/>
+      <c r="J551" s="33"/>
+      <c r="K551" s="33"/>
       <c r="L551" s="2"/>
       <c r="M551" s="1"/>
       <c r="N551" s="1"/>
@@ -16069,8 +16088,8 @@
       <c r="G552" s="1"/>
       <c r="H552" s="1"/>
       <c r="I552" s="1"/>
-      <c r="J552" s="1"/>
-      <c r="K552" s="1"/>
+      <c r="J552" s="33"/>
+      <c r="K552" s="33"/>
       <c r="L552" s="2"/>
       <c r="M552" s="1"/>
       <c r="N552" s="1"/>
@@ -16097,8 +16116,8 @@
       <c r="G553" s="1"/>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
-      <c r="J553" s="1"/>
-      <c r="K553" s="1"/>
+      <c r="J553" s="33"/>
+      <c r="K553" s="33"/>
       <c r="L553" s="2"/>
       <c r="M553" s="1"/>
       <c r="N553" s="1"/>
@@ -16125,8 +16144,8 @@
       <c r="G554" s="1"/>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
-      <c r="J554" s="1"/>
-      <c r="K554" s="1"/>
+      <c r="J554" s="33"/>
+      <c r="K554" s="33"/>
       <c r="L554" s="2"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
@@ -16153,8 +16172,8 @@
       <c r="G555" s="1"/>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
-      <c r="J555" s="1"/>
-      <c r="K555" s="1"/>
+      <c r="J555" s="33"/>
+      <c r="K555" s="33"/>
       <c r="L555" s="2"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
@@ -16181,8 +16200,8 @@
       <c r="G556" s="1"/>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
-      <c r="J556" s="1"/>
-      <c r="K556" s="1"/>
+      <c r="J556" s="33"/>
+      <c r="K556" s="33"/>
       <c r="L556" s="2"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
@@ -16209,8 +16228,8 @@
       <c r="G557" s="1"/>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
-      <c r="J557" s="1"/>
-      <c r="K557" s="1"/>
+      <c r="J557" s="33"/>
+      <c r="K557" s="33"/>
       <c r="L557" s="2"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
